--- a/results/consolidated/NF_GARCH_Results_manual.xlsx
+++ b/results/consolidated/NF_GARCH_Results_manual.xlsx
@@ -80,34 +80,34 @@
     <t xml:space="preserve">gjrGARCH</t>
   </si>
   <si>
+    <t xml:space="preserve">TGARCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WindowStart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WindowEnd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestStart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestEnd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssetType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS_CV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity</t>
+  </si>
+  <si>
     <t xml:space="preserve">eGARCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGARCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WindowStart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WindowEnd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TestStart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TestEnd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AssetType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TS_CV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity</t>
   </si>
   <si>
     <t xml:space="preserve">Avg_AIC</t>
@@ -602,10 +602,10 @@
         <v>15436.5575706349</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0000471221203664775</v>
+        <v>0.0000429924605098405</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00506340397644398</v>
+        <v>0.00490017529074978</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -631,10 +631,10 @@
         <v>15536.6553205405</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0000541902060297839</v>
+        <v>0.0000520595129536844</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00534488120657274</v>
+        <v>0.00528619064757042</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
@@ -660,10 +660,10 @@
         <v>12835.4618918238</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000151102849544144</v>
+        <v>0.000153700150191844</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0093812057061357</v>
+        <v>0.00936764893306355</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
@@ -689,10 +689,10 @@
         <v>8150.29805814787</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00134506210144947</v>
+        <v>0.00142634329904931</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0267916397053963</v>
+        <v>0.0272432424628154</v>
       </c>
       <c r="I5" t="s">
         <v>12</v>
@@ -718,10 +718,10 @@
         <v>10907.308175535</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000413129750487411</v>
+        <v>0.000409421267002899</v>
       </c>
       <c r="H6" t="n">
-        <v>0.014402843653106</v>
+        <v>0.0144130890260051</v>
       </c>
       <c r="I6" t="s">
         <v>12</v>
@@ -747,10 +747,10 @@
         <v>8785.54444202782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000852662289321726</v>
+        <v>0.000871937248769845</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0211827623315875</v>
+        <v>0.0212944310569644</v>
       </c>
       <c r="I7" t="s">
         <v>12</v>
@@ -776,10 +776,10 @@
         <v>16686.4152954809</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000468960991281148</v>
+        <v>0.000042881880258254</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00503851779434072</v>
+        <v>0.00488461971956549</v>
       </c>
       <c r="I8" t="s">
         <v>12</v>
@@ -805,10 +805,10 @@
         <v>16558.6700118246</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0000541989383920334</v>
+        <v>0.000052058658312496</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0053442522767311</v>
+        <v>0.0052840979932641</v>
       </c>
       <c r="I9" t="s">
         <v>12</v>
@@ -834,10 +834,10 @@
         <v>13796.2027317123</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00015096287634305</v>
+        <v>0.000153260125523895</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00934033768264938</v>
+        <v>0.00932006142463944</v>
       </c>
       <c r="I10" t="s">
         <v>12</v>
@@ -863,10 +863,10 @@
         <v>9453.10713795071</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00130997725605224</v>
+        <v>0.00139596012545205</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0263696420670088</v>
+        <v>0.0269213319681704</v>
       </c>
       <c r="I11" t="s">
         <v>12</v>
@@ -892,10 +892,10 @@
         <v>12251.0385138578</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000412427477910599</v>
+        <v>0.000408453415032372</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0143943179341497</v>
+        <v>0.0143806332568695</v>
       </c>
       <c r="I12" t="s">
         <v>12</v>
@@ -921,10 +921,10 @@
         <v>10792.9568311302</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000773198625882046</v>
+        <v>0.000793309046145127</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0196400882473723</v>
+        <v>0.019839182441553</v>
       </c>
       <c r="I13" t="s">
         <v>12</v>
@@ -950,10 +950,10 @@
         <v>17297.2571301008</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0000400626614373225</v>
+        <v>0.0000389270752310303</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00470925312283025</v>
+        <v>0.004634694296471</v>
       </c>
       <c r="I14" t="s">
         <v>12</v>
@@ -979,10 +979,10 @@
         <v>17068.3741774856</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0000515527973425671</v>
+        <v>0.0000511182550312698</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00525776264751765</v>
+        <v>0.0053035667901323</v>
       </c>
       <c r="I15" t="s">
         <v>12</v>
@@ -1008,10 +1008,10 @@
         <v>14349.7081110585</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000188423406765555</v>
+        <v>0.000179474887527678</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0105524299703285</v>
+        <v>0.0104374757850525</v>
       </c>
       <c r="I16" t="s">
         <v>12</v>
@@ -1037,10 +1037,10 @@
         <v>9910.00882021353</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00111959510690415</v>
+        <v>0.00113138411916276</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0241058175385153</v>
+        <v>0.0242058272469228</v>
       </c>
       <c r="I17" t="s">
         <v>12</v>
@@ -1066,10 +1066,10 @@
         <v>12626.8050283989</v>
       </c>
       <c r="G18" t="n">
-        <v>0.000372757634185981</v>
+        <v>0.000372110242411962</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0138921120121489</v>
+        <v>0.0137892412456215</v>
       </c>
       <c r="I18" t="s">
         <v>12</v>
@@ -1095,10 +1095,10 @@
         <v>11206.0417872593</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000695097935646265</v>
+        <v>0.000701667716945119</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0184203552407474</v>
+        <v>0.0186656908051118</v>
       </c>
       <c r="I19" t="s">
         <v>12</v>
@@ -1112,22 +1112,22 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>31837.7685390903</v>
+        <v>-32326.2491294199</v>
       </c>
       <c r="E20" t="n">
-        <v>31876.2595018854</v>
+        <v>-32287.7581666248</v>
       </c>
       <c r="F20" t="n">
-        <v>-15912.8842695452</v>
+        <v>16169.12456471</v>
       </c>
       <c r="G20" t="n">
-        <v>0.718525068301419</v>
+        <v>0.0000344213950678341</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0920867446967219</v>
+        <v>0.00423485074942777</v>
       </c>
       <c r="I20" t="s">
         <v>12</v>
@@ -1135,28 +1135,28 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>-32326.2491294199</v>
+        <v>-31954.3769009613</v>
       </c>
       <c r="E21" t="n">
-        <v>-32287.7581666248</v>
+        <v>-31915.8859381662</v>
       </c>
       <c r="F21" t="n">
-        <v>16169.12456471</v>
+        <v>15983.1884504807</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0000344245658589725</v>
+        <v>0.000040961652767101</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00423507712086083</v>
+        <v>0.00452963118836436</v>
       </c>
       <c r="I21" t="s">
         <v>12</v>
@@ -1164,28 +1164,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="n">
-        <v>-31954.3769009613</v>
+        <v>-26765.1554633125</v>
       </c>
       <c r="E22" t="n">
-        <v>-31915.8859381662</v>
+        <v>-26726.6645005174</v>
       </c>
       <c r="F22" t="n">
-        <v>15983.1884504807</v>
+        <v>13388.5777316562</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0000409777544596631</v>
+        <v>0.000117589911688175</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0045298303922697</v>
+        <v>0.00815181462650758</v>
       </c>
       <c r="I22" t="s">
         <v>12</v>
@@ -1193,28 +1193,28 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" t="n">
-        <v>-26765.1554633125</v>
+        <v>-17940.7188127727</v>
       </c>
       <c r="E23" t="n">
-        <v>-26726.6645005174</v>
+        <v>-17902.2278499776</v>
       </c>
       <c r="F23" t="n">
-        <v>13388.5777316562</v>
+        <v>8976.35940638635</v>
       </c>
       <c r="G23" t="n">
-        <v>0.00011769745293201</v>
+        <v>0.00101199956331745</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00815489849998383</v>
+        <v>0.0221733143992038</v>
       </c>
       <c r="I23" t="s">
         <v>12</v>
@@ -1222,28 +1222,28 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
         <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>-17940.7188127727</v>
+        <v>-23433.1284200857</v>
       </c>
       <c r="E24" t="n">
-        <v>-17902.2278499776</v>
+        <v>-23394.6374572906</v>
       </c>
       <c r="F24" t="n">
-        <v>8976.35940638635</v>
+        <v>11722.5642100428</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00100380132812952</v>
+        <v>0.00031699205138684</v>
       </c>
       <c r="H24" t="n">
-        <v>0.022140732321569</v>
+        <v>0.0121101815907052</v>
       </c>
       <c r="I24" t="s">
         <v>12</v>
@@ -1251,59 +1251,30 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D25" t="n">
-        <v>-23433.1284200857</v>
+        <v>-20521.2259010673</v>
       </c>
       <c r="E25" t="n">
-        <v>-23394.6374572906</v>
+        <v>-20482.7349382722</v>
       </c>
       <c r="F25" t="n">
-        <v>11722.5642100428</v>
+        <v>10266.6129505337</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000319284269996263</v>
+        <v>0.000597748561972406</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0121920750030135</v>
+        <v>0.0163970770677635</v>
       </c>
       <c r="I25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-20521.2259010673</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-20482.7349382722</v>
-      </c>
-      <c r="F26" t="n">
-        <v>10266.6129505337</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.00059953077463494</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.0164235828002378</v>
-      </c>
-      <c r="I26" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1320,16 +1291,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" t="s">
-        <v>25</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -1359,7 +1330,7 @@
         <v>2</v>
       </c>
       <c r="N1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -1391,19 +1362,19 @@
         <v>1790.94396160695</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0000167109683159141</v>
+        <v>0.0000168437069874028</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00323604210240459</v>
+        <v>0.00371096666186276</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
         <v>11</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1435,19 +1406,19 @@
         <v>1650.97943252573</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0000176939209284565</v>
+        <v>0.0000166653889276515</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00333105337048631</v>
+        <v>0.00339346434594281</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
         <v>11</v>
       </c>
       <c r="N3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -1479,19 +1450,19 @@
         <v>1722.99586538057</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0000620418524294945</v>
+        <v>0.0000612393513535588</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00658076831546724</v>
+        <v>0.00630523394863459</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
         <v>11</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -1523,19 +1494,19 @@
         <v>1741.11705625888</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0000262398816713506</v>
+        <v>0.0000252751275670387</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00411770853763819</v>
+        <v>0.00416283433298083</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
         <v>13</v>
       </c>
       <c r="N5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -1567,19 +1538,19 @@
         <v>1722.66928376473</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0000302759045022097</v>
+        <v>0.0000266863823801212</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00451611131158459</v>
+        <v>0.00452435313805251</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M6" t="s">
         <v>13</v>
       </c>
       <c r="N6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -1611,19 +1582,19 @@
         <v>1743.16853582652</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0000589608707272758</v>
+        <v>0.0000357761934308046</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00629922404919573</v>
+        <v>0.00459392305584012</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
         <v>13</v>
       </c>
       <c r="N7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -1655,19 +1626,19 @@
         <v>1423.49339639796</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0000804342508214846</v>
+        <v>0.000105418163814979</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00748577065069542</v>
+        <v>0.00844313020205049</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M8" t="s">
         <v>14</v>
       </c>
       <c r="N8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -1699,19 +1670,19 @@
         <v>1460.24604566354</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00014187356380203</v>
+        <v>0.000179060931446553</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00924930447709106</v>
+        <v>0.0109554066330273</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
         <v>14</v>
       </c>
       <c r="N9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -1743,19 +1714,19 @@
         <v>1462.28173788122</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0000968718819260811</v>
+        <v>0.000112725093878265</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00778723435963803</v>
+        <v>0.00884544181648316</v>
       </c>
       <c r="L10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
         <v>14</v>
       </c>
       <c r="N10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -1787,19 +1758,19 @@
         <v>892.668147276459</v>
       </c>
       <c r="J11" t="n">
-        <v>0.000874792179809386</v>
+        <v>0.00127356594242085</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0214215451659448</v>
+        <v>0.0267833957550578</v>
       </c>
       <c r="L11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M11" t="s">
         <v>15</v>
       </c>
       <c r="N11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -1831,19 +1802,19 @@
         <v>1153.19334159343</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000353948781867446</v>
+        <v>0.000323078956608417</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0144012023419427</v>
+        <v>0.0135934557761841</v>
       </c>
       <c r="L12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
         <v>15</v>
       </c>
       <c r="N12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -1875,19 +1846,19 @@
         <v>903.047466164125</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00145624845419443</v>
+        <v>0.00142563535601886</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0309143509344589</v>
+        <v>0.0301579861623953</v>
       </c>
       <c r="L13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
         <v>15</v>
       </c>
       <c r="N13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -1919,19 +1890,19 @@
         <v>848.782895758045</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00143178046398751</v>
+        <v>0.00148793484907472</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0351867135482878</v>
+        <v>0.0359678466336466</v>
       </c>
       <c r="L14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M14" t="s">
         <v>16</v>
       </c>
       <c r="N14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -1963,19 +1934,19 @@
         <v>1262.44155186695</v>
       </c>
       <c r="J15" t="n">
-        <v>0.000442946293641639</v>
+        <v>0.000358394081999158</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0163742716547675</v>
+        <v>0.0160973227384861</v>
       </c>
       <c r="L15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
         <v>16</v>
       </c>
       <c r="N15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2007,19 +1978,19 @@
         <v>1198.29605375955</v>
       </c>
       <c r="J16" t="n">
-        <v>0.000461518740129558</v>
+        <v>0.000299736816508904</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0169030122106642</v>
+        <v>0.0127919472571102</v>
       </c>
       <c r="L16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M16" t="s">
         <v>16</v>
       </c>
       <c r="N16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -2051,19 +2022,19 @@
         <v>829.158520078244</v>
       </c>
       <c r="J17" t="n">
-        <v>0.000791648945744198</v>
+        <v>0.00109151669904571</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0225134110131217</v>
+        <v>0.0254423639169758</v>
       </c>
       <c r="L17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M17" t="s">
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
@@ -2095,19 +2066,19 @@
         <v>1037.26781994567</v>
       </c>
       <c r="J18" t="n">
-        <v>0.00106966720704273</v>
+        <v>0.00107968750743617</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0221373506524419</v>
+        <v>0.0216932121908557</v>
       </c>
       <c r="L18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M18" t="s">
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -2139,19 +2110,19 @@
         <v>1025.93797076023</v>
       </c>
       <c r="J19" t="n">
-        <v>0.000633695794138548</v>
+        <v>0.000817514963357951</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0212763332127231</v>
+        <v>0.0235414586705738</v>
       </c>
       <c r="L19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M19" t="s">
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -2183,19 +2154,19 @@
         <v>1905.28251813616</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0000168525202167928</v>
+        <v>0.0000169323366389156</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00324005764559907</v>
+        <v>0.00374313440325629</v>
       </c>
       <c r="L20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M20" t="s">
         <v>11</v>
       </c>
       <c r="N20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -2227,19 +2198,19 @@
         <v>1819.83357435691</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0000181853907199457</v>
+        <v>0.000017491266107062</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0035722282461791</v>
+        <v>0.00340722709390911</v>
       </c>
       <c r="L21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M21" t="s">
         <v>11</v>
       </c>
       <c r="N21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -2271,19 +2242,19 @@
         <v>1939.02788164321</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0000465776886928858</v>
+        <v>0.0000455615656914589</v>
       </c>
       <c r="K22" t="n">
-        <v>0.00563412149395579</v>
+        <v>0.00524207338579668</v>
       </c>
       <c r="L22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M22" t="s">
         <v>11</v>
       </c>
       <c r="N22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -2315,19 +2286,19 @@
         <v>1892.46710646983</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0000263926265855201</v>
+        <v>0.0000254151479006736</v>
       </c>
       <c r="K23" t="n">
-        <v>0.00414885797567494</v>
+        <v>0.00416304645033549</v>
       </c>
       <c r="L23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M23" t="s">
         <v>13</v>
       </c>
       <c r="N23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -2359,19 +2330,19 @@
         <v>1906.08201179639</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0000228872698675581</v>
+        <v>0.0000199377439805045</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00412112119497133</v>
+        <v>0.00370038089221392</v>
       </c>
       <c r="L24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
         <v>13</v>
       </c>
       <c r="N24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
@@ -2403,19 +2374,19 @@
         <v>1843.87254070678</v>
       </c>
       <c r="J25" t="n">
-        <v>0.000058935755439247</v>
+        <v>0.0000358070751104555</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0062989806171093</v>
+        <v>0.00459572892908656</v>
       </c>
       <c r="L25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M25" t="s">
         <v>13</v>
       </c>
       <c r="N25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
@@ -2447,19 +2418,19 @@
         <v>1538.17027669921</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0000775451400576484</v>
+        <v>0.000101571202878723</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0072959239598892</v>
+        <v>0.00819894429017799</v>
       </c>
       <c r="L26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M26" t="s">
         <v>14</v>
       </c>
       <c r="N26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -2491,19 +2462,19 @@
         <v>1564.20037496712</v>
       </c>
       <c r="J27" t="n">
-        <v>0.000143731731326851</v>
+        <v>0.000181600272345284</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0091548542391462</v>
+        <v>0.0108996860699163</v>
       </c>
       <c r="L27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M27" t="s">
         <v>14</v>
       </c>
       <c r="N27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -2535,19 +2506,19 @@
         <v>1538.32624311452</v>
       </c>
       <c r="J28" t="n">
-        <v>0.000101638178604186</v>
+        <v>0.000118059967667197</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00800763874641177</v>
+        <v>0.00910827080522836</v>
       </c>
       <c r="L28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M28" t="s">
         <v>14</v>
       </c>
       <c r="N28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -2579,19 +2550,19 @@
         <v>1021.77570615141</v>
       </c>
       <c r="J29" t="n">
-        <v>0.000853874460451449</v>
+        <v>0.00125517719257519</v>
       </c>
       <c r="K29" t="n">
-        <v>0.020998721161339</v>
+        <v>0.0274059503934423</v>
       </c>
       <c r="L29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M29" t="s">
         <v>15</v>
       </c>
       <c r="N29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -2623,19 +2594,19 @@
         <v>1264.53034631883</v>
       </c>
       <c r="J30" t="n">
-        <v>0.000353360089086917</v>
+        <v>0.000321931261711761</v>
       </c>
       <c r="K30" t="n">
-        <v>0.014368776746323</v>
+        <v>0.0135941716821453</v>
       </c>
       <c r="L30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M30" t="s">
         <v>15</v>
       </c>
       <c r="N30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -2667,19 +2638,19 @@
         <v>975.844380256329</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00144984028768991</v>
+        <v>0.00142017156676126</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0309005998069728</v>
+        <v>0.0302500624932108</v>
       </c>
       <c r="L31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M31" t="s">
         <v>15</v>
       </c>
       <c r="N31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32">
@@ -2711,19 +2682,19 @@
         <v>1497.00010655199</v>
       </c>
       <c r="J32" t="n">
-        <v>0.000217623665522254</v>
+        <v>0.000223772267429541</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0119752022045961</v>
+        <v>0.0120241212853316</v>
       </c>
       <c r="L32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M32" t="s">
         <v>16</v>
       </c>
       <c r="N32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33">
@@ -2755,19 +2726,19 @@
         <v>1387.86716095206</v>
       </c>
       <c r="J33" t="n">
-        <v>0.000422425471196466</v>
+        <v>0.000328196801229786</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0159282456170785</v>
+        <v>0.0154800608358923</v>
       </c>
       <c r="L33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M33" t="s">
         <v>16</v>
       </c>
       <c r="N33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
@@ -2799,19 +2770,19 @@
         <v>1281.87544707222</v>
       </c>
       <c r="J34" t="n">
-        <v>0.000452945589110676</v>
+        <v>0.00029585398758452</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0168599009490246</v>
+        <v>0.0128224399125083</v>
       </c>
       <c r="L34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M34" t="s">
         <v>16</v>
       </c>
       <c r="N34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
@@ -2843,19 +2814,19 @@
         <v>1162.42408007151</v>
       </c>
       <c r="J35" t="n">
-        <v>0.000715815655911645</v>
+        <v>0.00101499554186125</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0180195699393733</v>
+        <v>0.0214476947195776</v>
       </c>
       <c r="L35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M35" t="s">
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
@@ -2887,19 +2858,19 @@
         <v>1250.17583366464</v>
       </c>
       <c r="J36" t="n">
-        <v>0.00110804907554669</v>
+        <v>0.00111815145145511</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0213712770526996</v>
+        <v>0.021944974267674</v>
       </c>
       <c r="L36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M36" t="s">
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
@@ -2931,19 +2902,19 @@
         <v>1173.04186687695</v>
       </c>
       <c r="J37" t="n">
-        <v>0.000657204007795499</v>
+        <v>0.000837886606165205</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0216334766000174</v>
+        <v>0.0241130794996143</v>
       </c>
       <c r="L37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M37" t="s">
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
@@ -2975,19 +2946,19 @@
         <v>1976.70411012366</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0000508052483589954</v>
+        <v>0.0000264188066341066</v>
       </c>
       <c r="K38" t="n">
-        <v>0.00564546278400887</v>
+        <v>0.0041932275460559</v>
       </c>
       <c r="L38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M38" t="s">
         <v>11</v>
       </c>
       <c r="N38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
@@ -3019,19 +2990,19 @@
         <v>1915.19126175902</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0000359539349078942</v>
+        <v>0.000032795164494103</v>
       </c>
       <c r="K39" t="n">
-        <v>0.00440102789122086</v>
+        <v>0.00450553977893627</v>
       </c>
       <c r="L39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M39" t="s">
         <v>11</v>
       </c>
       <c r="N39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
@@ -3063,19 +3034,19 @@
         <v>2019.98640030205</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0000620630034461469</v>
+        <v>0.0000679853178700105</v>
       </c>
       <c r="K40" t="n">
-        <v>0.00716794972681526</v>
+        <v>0.00656463726504158</v>
       </c>
       <c r="L40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M40" t="s">
         <v>11</v>
       </c>
       <c r="N40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
@@ -3107,19 +3078,19 @@
         <v>1976.59062080023</v>
       </c>
       <c r="J41" t="n">
-        <v>0.00005126114502596</v>
+        <v>0.0000316871329119361</v>
       </c>
       <c r="K41" t="n">
-        <v>0.00573826294318464</v>
+        <v>0.00434311682905901</v>
       </c>
       <c r="L41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M41" t="s">
         <v>13</v>
       </c>
       <c r="N41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
@@ -3151,19 +3122,19 @@
         <v>2005.33347057667</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0000307639851765271</v>
+        <v>0.0000175091867523393</v>
       </c>
       <c r="K42" t="n">
-        <v>0.00464394475910482</v>
+        <v>0.00322112510957158</v>
       </c>
       <c r="L42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M42" t="s">
         <v>13</v>
       </c>
       <c r="N42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
@@ -3195,19 +3166,19 @@
         <v>1909.47299286456</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0000556997512924068</v>
+        <v>0.0000536412572835241</v>
       </c>
       <c r="K43" t="n">
-        <v>0.00639080406931313</v>
+        <v>0.00619399386552167</v>
       </c>
       <c r="L43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M43" t="s">
         <v>13</v>
       </c>
       <c r="N43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44">
@@ -3239,19 +3210,19 @@
         <v>1604.13149840892</v>
       </c>
       <c r="J44" t="n">
-        <v>0.000103554489370186</v>
+        <v>0.000108926057019504</v>
       </c>
       <c r="K44" t="n">
-        <v>0.00761732212104187</v>
+        <v>0.00735457005957398</v>
       </c>
       <c r="L44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M44" t="s">
         <v>14</v>
       </c>
       <c r="N44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
@@ -3283,19 +3254,19 @@
         <v>1637.52241960652</v>
       </c>
       <c r="J45" t="n">
-        <v>0.000220094078095655</v>
+        <v>0.000200313012946207</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0116132219008434</v>
+        <v>0.01055897732451</v>
       </c>
       <c r="L45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M45" t="s">
         <v>14</v>
       </c>
       <c r="N45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
@@ -3327,19 +3298,19 @@
         <v>1604.44896612117</v>
       </c>
       <c r="J46" t="n">
-        <v>0.000159277098602454</v>
+        <v>0.000177271600950195</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0103726230645691</v>
+        <v>0.0114056548444473</v>
       </c>
       <c r="L46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M46" t="s">
         <v>14</v>
       </c>
       <c r="N46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
@@ -3371,19 +3342,19 @@
         <v>1103.48840048295</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0010563244794359</v>
+        <v>0.00164993185452594</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0250288675743383</v>
+        <v>0.0349659659232158</v>
       </c>
       <c r="L47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M47" t="s">
         <v>15</v>
       </c>
       <c r="N47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
@@ -3415,19 +3386,19 @@
         <v>1328.04810806444</v>
       </c>
       <c r="J48" t="n">
-        <v>0.000335918456242305</v>
+        <v>0.000352210173767422</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0146230330671403</v>
+        <v>0.0133269200478224</v>
       </c>
       <c r="L48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M48" t="s">
         <v>15</v>
       </c>
       <c r="N48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
@@ -3459,19 +3430,19 @@
         <v>1023.32647898534</v>
       </c>
       <c r="J49" t="n">
-        <v>0.00208720353529895</v>
+        <v>0.00287280463203175</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0322444027031829</v>
+        <v>0.0420341108391358</v>
       </c>
       <c r="L49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M49" t="s">
         <v>15</v>
       </c>
       <c r="N49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
@@ -3503,19 +3474,19 @@
         <v>1552.05743969721</v>
       </c>
       <c r="J50" t="n">
-        <v>0.000246137349105436</v>
+        <v>0.000173716742657723</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0112375209340916</v>
+        <v>0.0104600960795573</v>
       </c>
       <c r="L50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M50" t="s">
         <v>16</v>
       </c>
       <c r="N50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
@@ -3547,19 +3518,19 @@
         <v>1444.459147636</v>
       </c>
       <c r="J51" t="n">
-        <v>0.000429560882824255</v>
+        <v>0.000276007885580517</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0170364614289268</v>
+        <v>0.0130160733889124</v>
       </c>
       <c r="L51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M51" t="s">
         <v>16</v>
       </c>
       <c r="N51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52">
@@ -3591,19 +3562,19 @@
         <v>1328.48845871435</v>
       </c>
       <c r="J52" t="n">
-        <v>0.000710337888637957</v>
+        <v>0.000834625980206093</v>
       </c>
       <c r="K52" t="n">
-        <v>0.0219472094715232</v>
+        <v>0.0216791973712876</v>
       </c>
       <c r="L52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M52" t="s">
         <v>16</v>
       </c>
       <c r="N52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
@@ -3635,19 +3606,19 @@
         <v>1219.89414550014</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00101462053871826</v>
+        <v>0.00140687663506757</v>
       </c>
       <c r="K53" t="n">
-        <v>0.0229392599081481</v>
+        <v>0.0282752170182194</v>
       </c>
       <c r="L53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M53" t="s">
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
@@ -3679,19 +3650,19 @@
         <v>1313.68151222282</v>
       </c>
       <c r="J54" t="n">
-        <v>0.00153456263470244</v>
+        <v>0.00134081908979218</v>
       </c>
       <c r="K54" t="n">
-        <v>0.0274378810334423</v>
+        <v>0.0274862987882097</v>
       </c>
       <c r="L54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M54" t="s">
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55">
@@ -3723,19 +3694,19 @@
         <v>1221.68918899082</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00175683378137351</v>
+        <v>0.0018565709374622</v>
       </c>
       <c r="K55" t="n">
-        <v>0.0325703317557726</v>
+        <v>0.0337864095363904</v>
       </c>
       <c r="L55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M55" t="s">
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
@@ -3752,7 +3723,7 @@
         <v>520</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F56" t="s">
         <v>18</v>
@@ -3767,19 +3738,19 @@
         <v>-3855.73703601571</v>
       </c>
       <c r="J56" t="n">
-        <v>207185870231954258362288464084248</v>
+        <v>90312177456970403800240448428202</v>
       </c>
       <c r="K56" t="n">
-        <v>3218585872179953</v>
+        <v>2124996325491648</v>
       </c>
       <c r="L56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M56" t="s">
         <v>13</v>
       </c>
       <c r="N56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
@@ -3796,7 +3767,7 @@
         <v>520</v>
       </c>
       <c r="E57" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F57" t="s">
         <v>18</v>
@@ -3811,19 +3782,19 @@
         <v>1097.07004201251</v>
       </c>
       <c r="J57" t="n">
-        <v>0.00104139804494214</v>
+        <v>0.00173426040641301</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0259750495742901</v>
+        <v>0.0355908318835844</v>
       </c>
       <c r="L57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M57" t="s">
         <v>15</v>
       </c>
       <c r="N57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
@@ -3840,7 +3811,7 @@
         <v>4020</v>
       </c>
       <c r="E58" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F58" t="s">
         <v>18</v>
@@ -3855,19 +3826,19 @@
         <v>1000.45681674002</v>
       </c>
       <c r="J58" t="n">
-        <v>5210351289941901286008600426022206442620202606644668466620026802062480406660640844880260864686400626686020220262088026008244428262642604060602686262044844640848648046462044688226842026806428264080</v>
+        <v>1061569196478882535864604804806204282048848024004082480222824448642826882688680864666622206280004440022066680248060002626004848640246886246000804644444406864064884284080286048262266840480680028</v>
       </c>
       <c r="K58" t="n">
-        <v>22580330089781615240088442200406020462440208082240202626826246820406624844262288228688882864462668</v>
+        <v>230417279141291260080020482644406604808284004000602004842282882688804226066822468802084666260226</v>
       </c>
       <c r="L58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M58" t="s">
         <v>15</v>
       </c>
       <c r="N58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59">
@@ -3890,421 +3861,421 @@
         <v>18</v>
       </c>
       <c r="G59" t="n">
-        <v>8175.66039831932</v>
+        <v>-3705.53862395545</v>
       </c>
       <c r="H59" t="n">
-        <v>8200.94804690985</v>
+        <v>-3680.25097536491</v>
       </c>
       <c r="I59" t="n">
-        <v>-4081.83019915966</v>
+        <v>1858.76931197772</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0445734208773483</v>
+        <v>0.0000198288568968508</v>
       </c>
       <c r="K59" t="n">
-        <v>0.210543336104814</v>
+        <v>0.00379022945076881</v>
       </c>
       <c r="L59" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" t="s">
+        <v>11</v>
+      </c>
+      <c r="N59" t="s">
         <v>27</v>
-      </c>
-      <c r="M59" t="s">
-        <v>16</v>
-      </c>
-      <c r="N59" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1</v>
+        <v>1501</v>
       </c>
       <c r="B60" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="C60" t="n">
-        <v>501</v>
+        <v>2001</v>
       </c>
       <c r="D60" t="n">
-        <v>520</v>
+        <v>2020</v>
       </c>
       <c r="E60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F60" t="s">
         <v>18</v>
       </c>
       <c r="G60" t="n">
-        <v>-3705.53862395545</v>
+        <v>-3521.0043705216</v>
       </c>
       <c r="H60" t="n">
-        <v>-3680.25097536491</v>
+        <v>-3495.71672193107</v>
       </c>
       <c r="I60" t="n">
-        <v>1858.76931197772</v>
+        <v>1766.5021852608</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0000231987057290424</v>
+        <v>0.0000147085769534063</v>
       </c>
       <c r="K60" t="n">
-        <v>0.00419626775115468</v>
+        <v>0.00334705671257526</v>
       </c>
       <c r="L60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M60" t="s">
         <v>11</v>
       </c>
       <c r="N60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1501</v>
+        <v>3501</v>
       </c>
       <c r="B61" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="C61" t="n">
-        <v>2001</v>
+        <v>4001</v>
       </c>
       <c r="D61" t="n">
-        <v>2020</v>
+        <v>4020</v>
       </c>
       <c r="E61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F61" t="s">
         <v>18</v>
       </c>
       <c r="G61" t="n">
-        <v>-3521.0043705216</v>
+        <v>-3754.52156277661</v>
       </c>
       <c r="H61" t="n">
-        <v>-3495.71672193107</v>
+        <v>-3729.23391418607</v>
       </c>
       <c r="I61" t="n">
-        <v>1766.5021852608</v>
+        <v>1883.2607813883</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0000218569033019729</v>
+        <v>0.0000481285354537247</v>
       </c>
       <c r="K61" t="n">
-        <v>0.00385326758740712</v>
+        <v>0.00609184376818989</v>
       </c>
       <c r="L61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M61" t="s">
         <v>11</v>
       </c>
       <c r="N61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3501</v>
+        <v>1</v>
       </c>
       <c r="B62" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="C62" t="n">
-        <v>4001</v>
+        <v>501</v>
       </c>
       <c r="D62" t="n">
-        <v>4020</v>
+        <v>520</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F62" t="s">
         <v>18</v>
       </c>
       <c r="G62" t="n">
-        <v>-3754.52156277661</v>
+        <v>-3676.0201244237</v>
       </c>
       <c r="H62" t="n">
-        <v>-3729.23391418607</v>
+        <v>-3650.73247583317</v>
       </c>
       <c r="I62" t="n">
-        <v>1883.2607813883</v>
+        <v>1844.01006221185</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0000678939591404799</v>
+        <v>0.0000203098620769981</v>
       </c>
       <c r="K62" t="n">
-        <v>0.00729281528531646</v>
+        <v>0.00393241830727844</v>
       </c>
       <c r="L62" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" t="s">
+        <v>13</v>
+      </c>
+      <c r="N62" t="s">
         <v>27</v>
-      </c>
-      <c r="M62" t="s">
-        <v>11</v>
-      </c>
-      <c r="N62" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1</v>
+        <v>1501</v>
       </c>
       <c r="B63" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="C63" t="n">
-        <v>501</v>
+        <v>2001</v>
       </c>
       <c r="D63" t="n">
-        <v>520</v>
+        <v>2020</v>
       </c>
       <c r="E63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F63" t="s">
         <v>18</v>
       </c>
       <c r="G63" t="n">
-        <v>-3676.0201244237</v>
+        <v>-3728.42415812967</v>
       </c>
       <c r="H63" t="n">
-        <v>-3650.73247583317</v>
+        <v>-3703.13650953913</v>
       </c>
       <c r="I63" t="n">
-        <v>1844.01006221185</v>
+        <v>1870.21207906483</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0000206305025351592</v>
+        <v>0.0000196206498932503</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00383642875418488</v>
+        <v>0.00370717841975225</v>
       </c>
       <c r="L63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M63" t="s">
         <v>13</v>
       </c>
       <c r="N63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1501</v>
+        <v>3501</v>
       </c>
       <c r="B64" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="C64" t="n">
-        <v>2001</v>
+        <v>4001</v>
       </c>
       <c r="D64" t="n">
-        <v>2020</v>
+        <v>4020</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F64" t="s">
         <v>18</v>
       </c>
       <c r="G64" t="n">
-        <v>-3728.42415812967</v>
+        <v>-3580.13249755125</v>
       </c>
       <c r="H64" t="n">
-        <v>-3703.13650953913</v>
+        <v>-3554.84484896072</v>
       </c>
       <c r="I64" t="n">
-        <v>1870.21207906483</v>
+        <v>1796.06624877562</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0000169240021216789</v>
+        <v>0.0000365726007639072</v>
       </c>
       <c r="K64" t="n">
-        <v>0.00330412168142429</v>
+        <v>0.00516031544824114</v>
       </c>
       <c r="L64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M64" t="s">
         <v>13</v>
       </c>
       <c r="N64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3501</v>
+        <v>1</v>
       </c>
       <c r="B65" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="C65" t="n">
-        <v>4001</v>
+        <v>501</v>
       </c>
       <c r="D65" t="n">
-        <v>4020</v>
+        <v>520</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F65" t="s">
         <v>18</v>
       </c>
       <c r="G65" t="n">
-        <v>-3580.13249755125</v>
+        <v>-2969.97381863828</v>
       </c>
       <c r="H65" t="n">
-        <v>-3554.84484896072</v>
+        <v>-2944.68617004775</v>
       </c>
       <c r="I65" t="n">
-        <v>1796.06624877562</v>
+        <v>1490.98690931914</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0000303030437976544</v>
+        <v>0.0000691212954471039</v>
       </c>
       <c r="K65" t="n">
-        <v>0.00475933333933749</v>
+        <v>0.00651663562019009</v>
       </c>
       <c r="L65" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" t="s">
+        <v>14</v>
+      </c>
+      <c r="N65" t="s">
         <v>27</v>
-      </c>
-      <c r="M65" t="s">
-        <v>13</v>
-      </c>
-      <c r="N65" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1</v>
+        <v>1501</v>
       </c>
       <c r="B66" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>501</v>
+        <v>2001</v>
       </c>
       <c r="D66" t="n">
-        <v>520</v>
+        <v>2020</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F66" t="s">
         <v>18</v>
       </c>
       <c r="G66" t="n">
-        <v>-2969.97381863828</v>
+        <v>-3023.67684209273</v>
       </c>
       <c r="H66" t="n">
-        <v>-2944.68617004775</v>
+        <v>-2998.3891935022</v>
       </c>
       <c r="I66" t="n">
-        <v>1490.98690931914</v>
+        <v>1517.83842104637</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0000693445929284761</v>
+        <v>0.00013969784332422</v>
       </c>
       <c r="K66" t="n">
-        <v>0.00659077251801649</v>
+        <v>0.00858965736351952</v>
       </c>
       <c r="L66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M66" t="s">
         <v>14</v>
       </c>
       <c r="N66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1501</v>
+        <v>3501</v>
       </c>
       <c r="B67" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="C67" t="n">
-        <v>2001</v>
+        <v>4001</v>
       </c>
       <c r="D67" t="n">
-        <v>2020</v>
+        <v>4020</v>
       </c>
       <c r="E67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F67" t="s">
         <v>18</v>
       </c>
       <c r="G67" t="n">
-        <v>-3023.67684209273</v>
+        <v>-2991.2713741899</v>
       </c>
       <c r="H67" t="n">
-        <v>-2998.3891935022</v>
+        <v>-2965.98372559937</v>
       </c>
       <c r="I67" t="n">
-        <v>1517.83842104637</v>
+        <v>1501.63568709495</v>
       </c>
       <c r="J67" t="n">
-        <v>0.000135807274447306</v>
+        <v>0.0000818388235859707</v>
       </c>
       <c r="K67" t="n">
-        <v>0.00831640495986089</v>
+        <v>0.00775521429596314</v>
       </c>
       <c r="L67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M67" t="s">
         <v>14</v>
       </c>
       <c r="N67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3501</v>
+        <v>1</v>
       </c>
       <c r="B68" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="C68" t="n">
-        <v>4001</v>
+        <v>501</v>
       </c>
       <c r="D68" t="n">
-        <v>4020</v>
+        <v>520</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F68" t="s">
         <v>18</v>
       </c>
       <c r="G68" t="n">
-        <v>-2991.2713741899</v>
+        <v>-1936.22375198158</v>
       </c>
       <c r="H68" t="n">
-        <v>-2965.98372559937</v>
+        <v>-1910.93610339105</v>
       </c>
       <c r="I68" t="n">
-        <v>1501.63568709495</v>
+        <v>974.111875990789</v>
       </c>
       <c r="J68" t="n">
-        <v>0.000081885675839928</v>
+        <v>0.000941735201291371</v>
       </c>
       <c r="K68" t="n">
-        <v>0.00761991761968711</v>
+        <v>0.0227151347239364</v>
       </c>
       <c r="L68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N68" t="s">
         <v>28</v>
@@ -4312,398 +4283,354 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>1501</v>
       </c>
       <c r="B69" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="C69" t="n">
-        <v>501</v>
+        <v>2001</v>
       </c>
       <c r="D69" t="n">
-        <v>520</v>
+        <v>2020</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F69" t="s">
         <v>18</v>
       </c>
       <c r="G69" t="n">
-        <v>-1936.22375198158</v>
+        <v>-2417.15962681482</v>
       </c>
       <c r="H69" t="n">
-        <v>-1910.93610339105</v>
+        <v>-2391.87197822429</v>
       </c>
       <c r="I69" t="n">
-        <v>974.111875990789</v>
+        <v>1214.57981340741</v>
       </c>
       <c r="J69" t="n">
-        <v>0.00116984515139004</v>
+        <v>0.000339403474945139</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0269421102072115</v>
+        <v>0.0128744447328164</v>
       </c>
       <c r="L69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M69" t="s">
         <v>15</v>
       </c>
       <c r="N69" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1501</v>
+        <v>3501</v>
       </c>
       <c r="B70" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="C70" t="n">
-        <v>2001</v>
+        <v>4001</v>
       </c>
       <c r="D70" t="n">
-        <v>2020</v>
+        <v>4020</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F70" t="s">
         <v>18</v>
       </c>
       <c r="G70" t="n">
-        <v>-2417.15962681482</v>
+        <v>-1857.27668339855</v>
       </c>
       <c r="H70" t="n">
-        <v>-2391.87197822429</v>
+        <v>-1831.98903480802</v>
       </c>
       <c r="I70" t="n">
-        <v>1214.57981340741</v>
+        <v>934.638341699277</v>
       </c>
       <c r="J70" t="n">
-        <v>0.000248468819624166</v>
+        <v>0.00265508402361316</v>
       </c>
       <c r="K70" t="n">
-        <v>0.0118592471424138</v>
+        <v>0.0384448975475999</v>
       </c>
       <c r="L70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M70" t="s">
         <v>15</v>
       </c>
       <c r="N70" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3501</v>
+        <v>1</v>
       </c>
       <c r="B71" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="C71" t="n">
-        <v>4001</v>
+        <v>501</v>
       </c>
       <c r="D71" t="n">
-        <v>4020</v>
+        <v>520</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F71" t="s">
         <v>18</v>
       </c>
       <c r="G71" t="n">
-        <v>-1857.27668339855</v>
+        <v>-2865.13119380738</v>
       </c>
       <c r="H71" t="n">
-        <v>-1831.98903480802</v>
+        <v>-2839.84354521684</v>
       </c>
       <c r="I71" t="n">
-        <v>934.638341699277</v>
+        <v>1438.56559690369</v>
       </c>
       <c r="J71" t="n">
-        <v>0.00116326506141874</v>
+        <v>0.000138294497177359</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0276258387534971</v>
+        <v>0.00882523685522698</v>
       </c>
       <c r="L71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M71" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N71" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1</v>
+        <v>1501</v>
       </c>
       <c r="B72" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="C72" t="n">
-        <v>501</v>
+        <v>2001</v>
       </c>
       <c r="D72" t="n">
-        <v>520</v>
+        <v>2020</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F72" t="s">
         <v>18</v>
       </c>
       <c r="G72" t="n">
-        <v>-2865.13119380738</v>
+        <v>-2668.40414022124</v>
       </c>
       <c r="H72" t="n">
-        <v>-2839.84354521684</v>
+        <v>-2643.1164916307</v>
       </c>
       <c r="I72" t="n">
-        <v>1438.56559690369</v>
+        <v>1340.20207011062</v>
       </c>
       <c r="J72" t="n">
-        <v>0.000266768785483751</v>
+        <v>0.000350622893760695</v>
       </c>
       <c r="K72" t="n">
-        <v>0.0130072016644426</v>
+        <v>0.0147881644879688</v>
       </c>
       <c r="L72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M72" t="s">
         <v>16</v>
       </c>
       <c r="N72" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1501</v>
+        <v>3501</v>
       </c>
       <c r="B73" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="C73" t="n">
-        <v>2001</v>
+        <v>4001</v>
       </c>
       <c r="D73" t="n">
-        <v>2020</v>
+        <v>4020</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F73" t="s">
         <v>18</v>
       </c>
       <c r="G73" t="n">
-        <v>-2668.40414022124</v>
+        <v>-2462.46817472629</v>
       </c>
       <c r="H73" t="n">
-        <v>-2643.1164916307</v>
+        <v>-2437.18052613575</v>
       </c>
       <c r="I73" t="n">
-        <v>1340.20207011062</v>
+        <v>1237.23408736314</v>
       </c>
       <c r="J73" t="n">
-        <v>0.000389047542042115</v>
+        <v>0.000235978105363867</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0154759703035964</v>
+        <v>0.0123818948712395</v>
       </c>
       <c r="L73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M73" t="s">
         <v>16</v>
       </c>
       <c r="N73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3501</v>
+        <v>1</v>
       </c>
       <c r="B74" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="C74" t="n">
-        <v>4001</v>
+        <v>501</v>
       </c>
       <c r="D74" t="n">
-        <v>4020</v>
+        <v>520</v>
       </c>
       <c r="E74" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F74" t="s">
         <v>18</v>
       </c>
       <c r="G74" t="n">
-        <v>-2462.46817472629</v>
+        <v>-2178.45452577297</v>
       </c>
       <c r="H74" t="n">
-        <v>-2437.18052613575</v>
+        <v>-2153.16687718244</v>
       </c>
       <c r="I74" t="n">
-        <v>1237.23408736314</v>
+        <v>1095.22726288649</v>
       </c>
       <c r="J74" t="n">
-        <v>0.000415611514550348</v>
+        <v>0.000829346188078308</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0161596691001535</v>
+        <v>0.0178675477469557</v>
       </c>
       <c r="L74" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M74" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N74" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>1501</v>
       </c>
       <c r="B75" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="C75" t="n">
-        <v>501</v>
+        <v>2001</v>
       </c>
       <c r="D75" t="n">
-        <v>520</v>
+        <v>2020</v>
       </c>
       <c r="E75" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F75" t="s">
         <v>18</v>
       </c>
       <c r="G75" t="n">
-        <v>-2178.45452577297</v>
+        <v>-2385.17146520627</v>
       </c>
       <c r="H75" t="n">
-        <v>-2153.16687718244</v>
+        <v>-2359.88381661574</v>
       </c>
       <c r="I75" t="n">
-        <v>1095.22726288649</v>
+        <v>1198.58573260313</v>
       </c>
       <c r="J75" t="n">
-        <v>0.000768112712936887</v>
+        <v>0.0010641081552665</v>
       </c>
       <c r="K75" t="n">
-        <v>0.0164045416707012</v>
+        <v>0.0204173350449131</v>
       </c>
       <c r="L75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M75" t="s">
         <v>17</v>
       </c>
       <c r="N75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1501</v>
+        <v>3501</v>
       </c>
       <c r="B76" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="C76" t="n">
-        <v>2001</v>
+        <v>4001</v>
       </c>
       <c r="D76" t="n">
-        <v>2020</v>
+        <v>4020</v>
       </c>
       <c r="E76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F76" t="s">
         <v>18</v>
       </c>
       <c r="G76" t="n">
-        <v>-2385.17146520627</v>
+        <v>-2222.18389420002</v>
       </c>
       <c r="H76" t="n">
-        <v>-2359.88381661574</v>
+        <v>-2196.89624560949</v>
       </c>
       <c r="I76" t="n">
-        <v>1198.58573260313</v>
+        <v>1117.09194710001</v>
       </c>
       <c r="J76" t="n">
-        <v>0.00108387748437913</v>
+        <v>0.000913231873606344</v>
       </c>
       <c r="K76" t="n">
-        <v>0.020709756216638</v>
+        <v>0.025322129544689</v>
       </c>
       <c r="L76" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M76" t="s">
         <v>17</v>
       </c>
       <c r="N76" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>3501</v>
-      </c>
-      <c r="B77" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C77" t="n">
-        <v>4001</v>
-      </c>
-      <c r="D77" t="n">
-        <v>4020</v>
-      </c>
-      <c r="E77" t="s">
-        <v>21</v>
-      </c>
-      <c r="F77" t="s">
-        <v>18</v>
-      </c>
-      <c r="G77" t="n">
-        <v>-2222.18389420002</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-2196.89624560949</v>
-      </c>
-      <c r="I77" t="n">
-        <v>1117.09194710001</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.00060810629043592</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0.0217653058694194</v>
-      </c>
-      <c r="L77" t="s">
-        <v>27</v>
-      </c>
-      <c r="M77" t="s">
-        <v>17</v>
-      </c>
-      <c r="N77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -4748,7 +4675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -4763,10 +4690,10 @@
         <v>12751.0712189683</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000352619357668561</v>
+        <v>0.000353285522699967</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0112793660229891</v>
+        <v>0.0112661449369954</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
@@ -4777,28 +4704,28 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>31837.7685390903</v>
+        <v>-27474.0650181722</v>
       </c>
       <c r="D3" t="n">
-        <v>31876.2595018854</v>
+        <v>-27435.5740553771</v>
       </c>
       <c r="E3" t="n">
-        <v>-15912.8842695452</v>
+        <v>13743.0325090861</v>
       </c>
       <c r="F3" t="n">
-        <v>0.718525068301419</v>
+        <v>0.00041244704938497</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0920867446967219</v>
+        <v>0.0128394160282186</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I3" t="s">
         <v>37</v>
@@ -4806,25 +4733,25 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>-27474.0650181722</v>
+        <v>-23875.94181957</v>
       </c>
       <c r="D4" t="n">
-        <v>-27435.5740553771</v>
+        <v>-23850.2811777066</v>
       </c>
       <c r="E4" t="n">
-        <v>13743.0325090861</v>
+        <v>11941.970909785</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000411248257046974</v>
+        <v>0.000492742323079571</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0128229550886813</v>
+        <v>0.0137507962361948</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
@@ -4838,56 +4765,27 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>-23875.94181957</v>
+        <v>-26502.7968406522</v>
       </c>
       <c r="D5" t="n">
-        <v>-23850.2811777066</v>
+        <v>-26470.7210383229</v>
       </c>
       <c r="E5" t="n">
-        <v>11941.970909785</v>
+        <v>13256.3984203261</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000477211552866502</v>
+        <v>0.000474320541787366</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0136944560965404</v>
+        <v>0.0134383211340103</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-26502.7968406522</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-26470.7210383229</v>
-      </c>
-      <c r="E6" t="n">
-        <v>13256.3984203261</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.000457943545618014</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.0133545260003753</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4933,7 +4831,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -4948,10 +4846,10 @@
         <v>1448.86213412245</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000365608223450156</v>
+        <v>0.000439868414305455</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0122066094680257</v>
+        <v>0.0123626297189902</v>
       </c>
       <c r="H2" t="n">
         <v>18</v>
@@ -4962,28 +4860,28 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>2932.02018821142</v>
+        <v>1184.14011817545</v>
       </c>
       <c r="D3" t="n">
-        <v>2957.30783680195</v>
+        <v>1209.42776676599</v>
       </c>
       <c r="E3" t="n">
-        <v>-1460.01009410571</v>
+        <v>-586.070059087726</v>
       </c>
       <c r="F3" t="n">
-        <v>1302587822485475321502400684088804668480808404466442644480084208048620604440460266220840246424600484424080880848022084002866682848468406040408424848066266460262462064648066422884268084204682846020</v>
+        <v>353856398826294199780602040246828420024646800840648204628484808286446820442046828024008004602402642682644640824846646626624684422662842860028888222024428806844202644060680884800820680842226008</v>
       </c>
       <c r="G3" t="n">
-        <v>5645082522445403810022668800604080648660802028860808484284864280604486266848822882422228246648442</v>
+        <v>76805759713763748426480628842622404280200808280082240444240442042684204680888660828888666442866</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="s">
         <v>39</v>
@@ -5006,10 +4904,10 @@
         <v>1565.80636782538</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000552276237811958</v>
+        <v>0.000637783970441851</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0149253103964816</v>
+        <v>0.0157428406453038</v>
       </c>
       <c r="H4" t="n">
         <v>18</v>
@@ -5035,10 +4933,10 @@
         <v>1326.0382823616</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000447074997537763</v>
+        <v>0.000485375306236507</v>
       </c>
       <c r="G5" t="n">
-        <v>0.014096189328253</v>
+        <v>0.0145002079575644</v>
       </c>
       <c r="H5" t="n">
         <v>18</v>
@@ -5064,10 +4962,10 @@
         <v>1497.87763643367</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000374660255767897</v>
+        <v>0.000409917403060772</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0124183085664645</v>
+        <v>0.0128967248560732</v>
       </c>
       <c r="H6" t="n">
         <v>18</v>
@@ -5154,7 +5052,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -5176,11 +5074,11 @@
       </c>
       <c r="J2"/>
       <c r="K2" t="n">
-        <v>0.000352619357668561</v>
+        <v>0.000353285522699967</v>
       </c>
       <c r="L2"/>
       <c r="M2" t="n">
-        <v>0.0112793660229891</v>
+        <v>0.0112661449369954</v>
       </c>
       <c r="N2"/>
       <c r="O2"/>
@@ -5221,11 +5119,11 @@
       </c>
       <c r="J3"/>
       <c r="K3" t="n">
-        <v>0.000411248257046974</v>
+        <v>0.00041244704938497</v>
       </c>
       <c r="L3"/>
       <c r="M3" t="n">
-        <v>0.0128229550886813</v>
+        <v>0.0128394160282186</v>
       </c>
       <c r="N3"/>
       <c r="O3"/>
@@ -5236,10 +5134,10 @@
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -5266,11 +5164,11 @@
       </c>
       <c r="J4"/>
       <c r="K4" t="n">
-        <v>0.000457943545618014</v>
+        <v>0.000474320541787366</v>
       </c>
       <c r="L4"/>
       <c r="M4" t="n">
-        <v>0.0133545260003753</v>
+        <v>0.0134383211340103</v>
       </c>
       <c r="N4"/>
       <c r="O4"/>
@@ -5281,10 +5179,10 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -5311,11 +5209,11 @@
       </c>
       <c r="J5"/>
       <c r="K5" t="n">
-        <v>0.000477211552866502</v>
+        <v>0.000492742323079571</v>
       </c>
       <c r="L5"/>
       <c r="M5" t="n">
-        <v>0.0136944560965404</v>
+        <v>0.0137507962361948</v>
       </c>
       <c r="N5"/>
       <c r="O5"/>
@@ -5326,10 +5224,10 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -5339,30 +5237,30 @@
       <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6"/>
-      <c r="E6" t="n">
-        <v>31837.7685390903</v>
-      </c>
-      <c r="F6"/>
-      <c r="G6" t="n">
-        <v>31876.2595018854</v>
-      </c>
-      <c r="H6"/>
-      <c r="I6" t="n">
-        <v>-15912.8842695452</v>
-      </c>
-      <c r="J6"/>
-      <c r="K6" t="n">
-        <v>0.718525068301419</v>
-      </c>
-      <c r="L6"/>
-      <c r="M6" t="n">
-        <v>0.0920867446967219</v>
-      </c>
-      <c r="N6"/>
+      <c r="C6"/>
+      <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6"/>
+      <c r="F6" t="n">
+        <v>-2885.72426824491</v>
+      </c>
+      <c r="G6"/>
+      <c r="H6" t="n">
+        <v>-2860.43661965437</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6" t="n">
+        <v>1448.86213412245</v>
+      </c>
+      <c r="K6"/>
+      <c r="L6" t="n">
+        <v>0.000439868414305455</v>
+      </c>
+      <c r="M6"/>
+      <c r="N6" t="n">
+        <v>0.0123626297189902</v>
+      </c>
       <c r="O6"/>
       <c r="P6"/>
       <c r="Q6"/>
@@ -5371,42 +5269,42 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="n">
-        <v>-2885.72426824491</v>
+        <v>1184.14011817545</v>
       </c>
       <c r="G7"/>
       <c r="H7" t="n">
-        <v>-2860.43661965437</v>
+        <v>1209.42776676599</v>
       </c>
       <c r="I7"/>
       <c r="J7" t="n">
-        <v>1448.86213412245</v>
+        <v>-586.070059087726</v>
       </c>
       <c r="K7"/>
       <c r="L7" t="n">
-        <v>0.000365608223450156</v>
+        <v>353856398826294199780602040246828420024646800840648204628484808286446820442046828024008004602402642682644640824846646626624684422662842860028888222024428806844202644060680884800820680842226008</v>
       </c>
       <c r="M7"/>
       <c r="N7" t="n">
-        <v>0.0122066094680257</v>
+        <v>76805759713763748426480628842622404280200808280082240444240442042684204680888660828888666442866</v>
       </c>
       <c r="O7"/>
       <c r="P7"/>
@@ -5416,42 +5314,42 @@
         <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U7" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="n">
-        <v>2932.02018821142</v>
+        <v>-3119.61273565076</v>
       </c>
       <c r="G8"/>
       <c r="H8" t="n">
-        <v>2957.30783680195</v>
+        <v>-3094.32508706023</v>
       </c>
       <c r="I8"/>
       <c r="J8" t="n">
-        <v>-1460.01009410571</v>
+        <v>1565.80636782538</v>
       </c>
       <c r="K8"/>
       <c r="L8" t="n">
-        <v>1302587822485475321502400684088804668480808404466442644480084208048620604440460266220840246424600484424080880848022084002866682848468406040408424848066266460262462064648066422884268084204682846020</v>
+        <v>0.000637783970441851</v>
       </c>
       <c r="M8"/>
       <c r="N8" t="n">
-        <v>5645082522445403810022668800604080648660802028860808484284864280604486266848822882422228246648442</v>
+        <v>0.0157428406453038</v>
       </c>
       <c r="O8"/>
       <c r="P8"/>
@@ -5461,18 +5359,18 @@
         <v>7</v>
       </c>
       <c r="T8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="n">
@@ -5480,23 +5378,23 @@
       </c>
       <c r="E9"/>
       <c r="F9" t="n">
-        <v>-3119.61273565076</v>
+        <v>-2644.0765647232</v>
       </c>
       <c r="G9"/>
       <c r="H9" t="n">
-        <v>-3094.32508706023</v>
+        <v>-2627.21813232951</v>
       </c>
       <c r="I9"/>
       <c r="J9" t="n">
-        <v>1565.80636782538</v>
+        <v>1326.0382823616</v>
       </c>
       <c r="K9"/>
       <c r="L9" t="n">
-        <v>0.000552276237811958</v>
+        <v>0.000485375306236507</v>
       </c>
       <c r="M9"/>
       <c r="N9" t="n">
-        <v>0.0149253103964816</v>
+        <v>0.0145002079575644</v>
       </c>
       <c r="O9"/>
       <c r="P9"/>
@@ -5506,10 +5404,10 @@
         <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="10">
@@ -5517,7 +5415,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="n">
@@ -5525,23 +5423,23 @@
       </c>
       <c r="E10"/>
       <c r="F10" t="n">
-        <v>-2644.0765647232</v>
+        <v>-2985.75527286734</v>
       </c>
       <c r="G10"/>
       <c r="H10" t="n">
-        <v>-2627.21813232951</v>
+        <v>-2964.68223237523</v>
       </c>
       <c r="I10"/>
       <c r="J10" t="n">
-        <v>1326.0382823616</v>
+        <v>1497.87763643367</v>
       </c>
       <c r="K10"/>
       <c r="L10" t="n">
-        <v>0.000447074997537763</v>
+        <v>0.000409917403060772</v>
       </c>
       <c r="M10"/>
       <c r="N10" t="n">
-        <v>0.014096189328253</v>
+        <v>0.0128967248560732</v>
       </c>
       <c r="O10"/>
       <c r="P10"/>
@@ -5551,54 +5449,9 @@
         <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11"/>
-      <c r="D11" t="n">
-        <v>18</v>
-      </c>
-      <c r="E11"/>
-      <c r="F11" t="n">
-        <v>-2985.75527286734</v>
-      </c>
-      <c r="G11"/>
-      <c r="H11" t="n">
-        <v>-2964.68223237523</v>
-      </c>
-      <c r="I11"/>
-      <c r="J11" t="n">
-        <v>1497.87763643367</v>
-      </c>
-      <c r="K11"/>
-      <c r="L11" t="n">
-        <v>0.000374660255767897</v>
-      </c>
-      <c r="M11"/>
-      <c r="N11" t="n">
-        <v>0.0124183085664645</v>
-      </c>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11"/>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
         <v>-8</v>
       </c>
     </row>
@@ -5650,107 +5503,107 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0000409777544596631</v>
+        <v>0.0000520590856330902</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0045298303922697</v>
+        <v>0.00528514432041726</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000226191828181642</v>
+        <v>0.0000281496117282663</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00396662792498222</v>
+        <v>0.00429004446641824</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000018358571641499</v>
+        <v>0.0000239094739048239</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000563202467287485</v>
+        <v>0.000995099853999024</v>
       </c>
       <c r="J2" t="n">
-        <v>44.801312037658</v>
+        <v>45.9275717467199</v>
       </c>
       <c r="K2" t="n">
-        <v>12.4331910582923</v>
+        <v>18.828243727514</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0000470091097472961</v>
+        <v>0.000040961652767101</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00505096088539235</v>
+        <v>0.00452963118836436</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000296770568839149</v>
+        <v>0.0000255010375780519</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00426571186234868</v>
+        <v>0.00426663739175728</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0000173320528633813</v>
+        <v>0.0000154606151890491</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000785249023043673</v>
+        <v>0.000262993796607078</v>
       </c>
       <c r="J3" t="n">
-        <v>36.8695619988382</v>
+        <v>37.7441195475066</v>
       </c>
       <c r="K3" t="n">
-        <v>15.5465274996418</v>
+        <v>5.80607527788692</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00132751967875086</v>
+        <v>0.0000511182550312698</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0265806408862026</v>
+        <v>0.0053035667901323</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000890344042183257</v>
+        <v>0.0000342791923159331</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0221675326928302</v>
+        <v>0.00458607860138409</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000437175636567598</v>
+        <v>0.0000168390627153366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00441310819337238</v>
+        <v>0.000717488188748217</v>
       </c>
       <c r="J4" t="n">
-        <v>32.9317631644424</v>
+        <v>32.9413879738968</v>
       </c>
       <c r="K4" t="n">
-        <v>16.6027155337068</v>
+        <v>13.528408656664</v>
       </c>
     </row>
     <row r="5">
@@ -5758,34 +5611,34 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0000541945722109087</v>
+        <v>0.0000429371703840473</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00534456674165192</v>
+        <v>0.00489239750515764</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000372820514655269</v>
+        <v>0.0000291222692843416</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00491700061436235</v>
+        <v>0.00430034997323371</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0000169125207453818</v>
+        <v>0.0000138149010997057</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000427566127289574</v>
+        <v>0.000592047531923929</v>
       </c>
       <c r="J5" t="n">
-        <v>31.2070380029266</v>
+        <v>32.1746891472811</v>
       </c>
       <c r="K5" t="n">
-        <v>8.00001474314866</v>
+        <v>12.10137833853</v>
       </c>
     </row>
     <row r="6">
@@ -5793,209 +5646,209 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000151032862943597</v>
+        <v>0.00141115171225068</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00936077169439254</v>
+        <v>0.0270822872154929</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000107015791089713</v>
+        <v>0.00100326004601606</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00816345440547861</v>
+        <v>0.0236308370437393</v>
       </c>
       <c r="G6" t="n">
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0000440170718538836</v>
+        <v>0.000407891666234628</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00119731728891393</v>
+        <v>0.00345145017175361</v>
       </c>
       <c r="J6" t="n">
-        <v>29.1440359376103</v>
+        <v>28.9048769663519</v>
       </c>
       <c r="K6" t="n">
-        <v>12.7907968274792</v>
+        <v>12.7443082790258</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00011769745293201</v>
+        <v>0.00031699205138684</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00815489849998383</v>
+        <v>0.0121101815907052</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0000956791810719033</v>
+        <v>0.00024163183210064</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00750903169918816</v>
+        <v>0.0119984320714784</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000022018271860107</v>
+        <v>0.0000753602192862003</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000645866800795665</v>
+        <v>0.000111749519226769</v>
       </c>
       <c r="J7" t="n">
-        <v>18.7075177173343</v>
+        <v>23.7735359471947</v>
       </c>
       <c r="K7" t="n">
-        <v>7.91998577047827</v>
+        <v>0.922773274618267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000188423406765555</v>
+        <v>0.0000344213950678341</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0105524299703285</v>
+        <v>0.00423485074942777</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000160975222022765</v>
+        <v>0.0000275553231013273</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00986772236215145</v>
+        <v>0.00440970997717799</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0000274481847427899</v>
+        <v>0.00000686607196650686</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000684707608177064</v>
+        <v>-0.000174859227750218</v>
       </c>
       <c r="J8" t="n">
-        <v>14.5672903456959</v>
+        <v>19.9471054353721</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4886249906641</v>
+        <v>-4.12905290166002</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00100380132812952</v>
+        <v>0.000117589911688175</v>
       </c>
       <c r="D9" t="n">
-        <v>0.022140732321569</v>
+        <v>0.00815181462650758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000860526344144317</v>
+        <v>0.0000968859874524315</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0221423987010408</v>
+        <v>0.00762050242655758</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000143274983985202</v>
+        <v>0.0000207039242357433</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0000016663794717639</v>
+        <v>0.000531312199949993</v>
       </c>
       <c r="J9" t="n">
-        <v>14.2732411255304</v>
+        <v>17.606888157758</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.00752630693312954</v>
+        <v>6.51771690467917</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0000515527973425671</v>
+        <v>0.000153480137857869</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00525776264751765</v>
+        <v>0.00934385517885149</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000459082938316313</v>
+        <v>0.0001330726053385</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00559100392386753</v>
+        <v>0.0094084799694806</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00000564450351093586</v>
+        <v>0.0000204075325193695</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.000333241276349879</v>
+        <v>-0.0000646247906291048</v>
       </c>
       <c r="J10" t="n">
-        <v>10.9489761989602</v>
+        <v>13.2965299642016</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.33808139869556</v>
+        <v>-0.691628769839819</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000812930457601886</v>
+        <v>0.000179474887527678</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0204114252894799</v>
+        <v>0.0104374757850525</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000829346781029884</v>
+        <v>0.000162170223638635</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0211585697450629</v>
+        <v>0.00977306740951042</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0000164163234279984</v>
+        <v>0.0000173046638890433</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.000747144455582976</v>
+        <v>0.000664408375542037</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.01940070943164</v>
+        <v>9.6418301899616</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.66042275336871</v>
+        <v>6.36560399491933</v>
       </c>
     </row>
     <row r="12">
@@ -6003,244 +5856,244 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00111959510690415</v>
+        <v>0.0000389270752310303</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0241058175385153</v>
+        <v>0.004634694296471</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00115981549032572</v>
+        <v>0.0000423997629994067</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0239654344482205</v>
+        <v>0.00508780153001125</v>
       </c>
       <c r="G12" t="n">
         <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0000402203834215678</v>
+        <v>-0.0000034726877683764</v>
       </c>
       <c r="I12" t="n">
-        <v>0.000140383090294773</v>
+        <v>-0.000453107233540252</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.59240435882068</v>
+        <v>-8.92100870092645</v>
       </c>
       <c r="K12" t="n">
-        <v>0.582361872068741</v>
+        <v>-9.77642115220549</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0000344245658589725</v>
+        <v>0.000372110242411962</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00423507712086083</v>
+        <v>0.0137892412456215</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0000376498560571651</v>
+        <v>0.000428116869481444</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00511411687462609</v>
+        <v>0.0150517889465858</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0000032252901981926</v>
+        <v>-0.0000560066270694823</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.000879039753765254</v>
+        <v>-0.00126254770096433</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.36915286428212</v>
+        <v>-15.0510845136796</v>
       </c>
       <c r="K13" t="n">
-        <v>-20.7561687468534</v>
+        <v>-9.1560346104267</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.000319284269996263</v>
+        <v>0.000832623147457486</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0121920750030135</v>
+        <v>0.0205668067492587</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000357142614025405</v>
+        <v>0.000993292128220233</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0148809470227308</v>
+        <v>0.0230304638775452</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0000378583440291421</v>
+        <v>-0.000160668980762747</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.00268887201971734</v>
+        <v>-0.00246365712828648</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.8572531085184</v>
+        <v>-19.2967228035119</v>
       </c>
       <c r="K14" t="n">
-        <v>-22.0542608132967</v>
+        <v>-11.9788023406953</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0000400626614373225</v>
+        <v>0.000408937341017636</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00470925312283025</v>
+        <v>0.0143968611414373</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000496073955710121</v>
+        <v>0.000498981467304438</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00573814680068166</v>
+        <v>0.0175306231104958</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.00000954473413368967</v>
+        <v>-0.0000900441262868026</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.00102889367785141</v>
+        <v>-0.00313376196905855</v>
       </c>
       <c r="J15" t="n">
-        <v>-23.8245133779299</v>
+        <v>-22.019052127333</v>
       </c>
       <c r="K15" t="n">
-        <v>-21.8483409367694</v>
+        <v>-21.7669805818916</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000372757634185981</v>
+        <v>0.00101199956331745</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0138921120121489</v>
+        <v>0.0221733143992038</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000462012040189216</v>
+        <v>0.00131207423328322</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0167403972781805</v>
+        <v>0.0246781590014509</v>
       </c>
       <c r="G16" t="n">
         <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0000892544060032347</v>
+        <v>-0.000300074669965776</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0028482852660316</v>
+        <v>-0.0025048446022471</v>
       </c>
       <c r="J16" t="n">
-        <v>-23.9443536007374</v>
+        <v>-29.6516600246445</v>
       </c>
       <c r="K16" t="n">
-        <v>-20.5028959134559</v>
+        <v>-11.29666299386</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00059953077463494</v>
+        <v>0.00113138411916276</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0164235828002378</v>
+        <v>0.0242058272469228</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000820032162583979</v>
+        <v>0.00162498222010837</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0196265345855862</v>
+        <v>0.0301089989367247</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.000220501387949038</v>
+        <v>-0.000493598100945607</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.00320295178534841</v>
+        <v>-0.00590317168980185</v>
       </c>
       <c r="J17" t="n">
-        <v>-36.7789940530248</v>
+        <v>-43.627808856896</v>
       </c>
       <c r="K17" t="n">
-        <v>-19.5021501964969</v>
+        <v>-24.3873990737181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.000412778614199005</v>
+        <v>0.000597748561972406</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0143985807936278</v>
+        <v>0.0163970770677635</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000571540037264683</v>
+        <v>0.000935562072317052</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0188712243640698</v>
+        <v>0.0212023374455193</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.000158761423065679</v>
+        <v>-0.000337813510344646</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.00447264357044194</v>
+        <v>-0.0048052603777558</v>
       </c>
       <c r="J18" t="n">
-        <v>-38.4616396306661</v>
+        <v>-56.5143158571481</v>
       </c>
       <c r="K18" t="n">
-        <v>-31.0630862482039</v>
+        <v>-29.3055912215166</v>
       </c>
     </row>
     <row r="19">
@@ -6251,49 +6104,51 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>0.000695097935646265</v>
+        <v>0.000701667716945119</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0184203552407474</v>
+        <v>0.0186656908051118</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0014353389849314</v>
+        <v>0.00153475555410732</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0276491575657876</v>
+        <v>0.0298493084476065</v>
       </c>
       <c r="G19" t="n">
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.000740241049285137</v>
+        <v>-0.000833087837162197</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.00922880232504028</v>
+        <v>-0.0111836176424947</v>
       </c>
       <c r="J19" t="n">
-        <v>-106.494496864949</v>
+        <v>-118.729680309256</v>
       </c>
       <c r="K19" t="n">
-        <v>-50.1011093674534</v>
+        <v>-59.9153696440314</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.718525068301419</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.0920867446967219</v>
-      </c>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
+        <v>13</v>
+      </c>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20" t="n">
+        <v>90312177456970403800240448428202</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2124996325491648</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20"/>
@@ -6301,72 +6156,26 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21" t="n">
-        <v>207185870231954258362288464084248</v>
+        <v>530784598239441267982802402408602646024424062002046240666462224826468446844840482888866608640002220066088840624080006868002424820628448628000402822222208482082442642040648024686688420240840064</v>
       </c>
       <c r="F21" t="n">
-        <v>3218585872179953</v>
+        <v>115208639570645630040060246822208802404642002000806002426646446844402668088466284406042888680668</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22" t="n">
-        <v>0.0445734208773483</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.210543336104814</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-      <c r="K22"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23" t="n">
-        <v>2605175644970950643004800268066608226860606808822884288860068406086240208880820422440680482848200868848060660686044068004622264686826802080806848686022422820424824028286022844668426068408264682040</v>
-      </c>
-      <c r="F23" t="n">
-        <v>11290165044890807620044226600208060286220604046620606868468628460208862422686644664844446482286884</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-      <c r="K23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6413,13 +6222,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000352619357668561</v>
+        <v>0.000353285522699967</v>
       </c>
       <c r="D2"/>
       <c r="E2" t="n">
@@ -6443,17 +6252,17 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000411248257046974</v>
+        <v>0.00041244704938497</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -6467,17 +6276,17 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000457943545618014</v>
+        <v>0.000474320541787366</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
@@ -6491,17 +6300,17 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000477211552866502</v>
+        <v>0.000492742323079571</v>
       </c>
       <c r="D5"/>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
@@ -6514,18 +6323,18 @@
       <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.718525068301419</v>
-      </c>
-      <c r="D6"/>
+      <c r="C6"/>
+      <c r="D6" t="n">
+        <v>0.000439868414305455</v>
+      </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
@@ -6533,23 +6342,23 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="n">
-        <v>0.000365608223450156</v>
+        <v>353856398826294199780602040246828420024646800840648204628484808286446820442046828024008004602402642682644640824846646626624684422662842860028888222024428806844202644060680884800820680842226008</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
@@ -6557,23 +6366,23 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="n">
-        <v>1302587822485475321502400684088804668480808404466442644480084208048620604440460266220840246424600484424080880848022084002866682848468406040408424848066266460262462064648066422884268084204682846020</v>
+        <v>0.000637783970441851</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
@@ -6581,23 +6390,23 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.000552276237811958</v>
+        <v>0.000485375306236507</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
@@ -6608,48 +6417,24 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="n">
-        <v>0.000447074997537763</v>
+        <v>0.000409917403060772</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11"/>
-      <c r="D11" t="n">
-        <v>0.000374660255767897</v>
-      </c>
-      <c r="E11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results/consolidated/NF_GARCH_Results_manual.xlsx
+++ b/results/consolidated/NF_GARCH_Results_manual.xlsx
@@ -492,13 +492,13 @@
         <v>9690.38318700543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0000221851439955279</v>
+        <v>0.0000221142231310187</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00350680323984356</v>
+        <v>0.00350130435394098</v>
       </c>
       <c r="I2" t="n">
-        <v>6069.98902615671</v>
+        <v>6150.84566075275</v>
       </c>
       <c r="J2" t="n">
         <v>1000</v>
@@ -527,13 +527,13 @@
         <v>10050.9916224586</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0000343156412396789</v>
+        <v>0.0000342891762629105</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00431129651580529</v>
+        <v>0.00430715491474091</v>
       </c>
       <c r="I3" t="n">
-        <v>5508.82107023185</v>
+        <v>5621.62603480591</v>
       </c>
       <c r="J3" t="n">
         <v>1000</v>
@@ -562,13 +562,13 @@
         <v>8359.6817151687</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0000984768223493641</v>
+        <v>0.0000982646535001163</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0076711107135781</v>
+        <v>0.00766466973784182</v>
       </c>
       <c r="I4" t="n">
-        <v>4624.79010082795</v>
+        <v>4687.23420538713</v>
       </c>
       <c r="J4" t="n">
         <v>1000</v>
@@ -597,13 +597,13 @@
         <v>5428.81494681033</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00112784864130891</v>
+        <v>0.00112544275340769</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0243489884030784</v>
+        <v>0.0243310309199076</v>
       </c>
       <c r="I5" t="n">
-        <v>2403.54090734104</v>
+        <v>2329.32045369707</v>
       </c>
       <c r="J5" t="n">
         <v>1000</v>
@@ -632,13 +632,13 @@
         <v>6961.90946770692</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000380230467021281</v>
+        <v>0.000377390286559431</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0138357256132259</v>
+        <v>0.0137695685839832</v>
       </c>
       <c r="I6" t="n">
-        <v>3340.03634885989</v>
+        <v>3216.14075778238</v>
       </c>
       <c r="J6" t="n">
         <v>1000</v>
@@ -667,13 +667,13 @@
         <v>5544.76166187601</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000564899217041747</v>
+        <v>0.000556982610417858</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0173084394110602</v>
+        <v>0.0171338026248393</v>
       </c>
       <c r="I7" t="n">
-        <v>3197.19453641434</v>
+        <v>3410.28943382607</v>
       </c>
       <c r="J7" t="n">
         <v>1000</v>
@@ -702,13 +702,13 @@
         <v>10548.1114072935</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000220510840146664</v>
+        <v>0.0000221028496511079</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00349987101066586</v>
+        <v>0.00350398158196061</v>
       </c>
       <c r="I8" t="n">
-        <v>6118.37105675463</v>
+        <v>6149.66082564719</v>
       </c>
       <c r="J8" t="n">
         <v>1000</v>
@@ -737,13 +737,13 @@
         <v>10728.2179537666</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0000343276839267905</v>
+        <v>0.0000343323132413725</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00431332375458778</v>
+        <v>0.00431244834374611</v>
       </c>
       <c r="I9" t="n">
-        <v>5567.2927690699</v>
+        <v>5513.45412415785</v>
       </c>
       <c r="J9" t="n">
         <v>1000</v>
@@ -772,13 +772,13 @@
         <v>8925.63372092964</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0000979807917381879</v>
+        <v>0.000097968589463147</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00761451440952866</v>
+        <v>0.007610469739582</v>
       </c>
       <c r="I10" t="n">
-        <v>4657.27240128892</v>
+        <v>4678.15826661324</v>
       </c>
       <c r="J10" t="n">
         <v>1000</v>
@@ -807,13 +807,13 @@
         <v>6314.14340259809</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00111584116890359</v>
+        <v>0.00111656063919218</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0242809822999104</v>
+        <v>0.0243001199699729</v>
       </c>
       <c r="I11" t="n">
-        <v>2479.46271077162</v>
+        <v>2332.57302733221</v>
       </c>
       <c r="J11" t="n">
         <v>1000</v>
@@ -842,13 +842,13 @@
         <v>8098.89143855781</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000356907004902563</v>
+        <v>0.00035741869281663</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0132975095651664</v>
+        <v>0.0133076321689625</v>
       </c>
       <c r="I12" t="n">
-        <v>3455.28097560578</v>
+        <v>3392.31545946402</v>
       </c>
       <c r="J12" t="n">
         <v>1000</v>
@@ -877,13 +877,13 @@
         <v>6957.63096377799</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000498873149339661</v>
+        <v>0.000497409451221445</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0158556355346086</v>
+        <v>0.0158462756380001</v>
       </c>
       <c r="I13" t="n">
-        <v>3568.86515662829</v>
+        <v>3642.44767713648</v>
       </c>
       <c r="J13" t="n">
         <v>1000</v>
@@ -912,13 +912,13 @@
         <v>10615.7142367279</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0000221493745717122</v>
+        <v>0.000022072815914142</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00350754493015052</v>
+        <v>0.00350164442843429</v>
       </c>
       <c r="I14" t="n">
-        <v>6230.29599769596</v>
+        <v>6197.99496720381</v>
       </c>
       <c r="J14" t="n">
         <v>1000</v>
@@ -947,13 +947,13 @@
         <v>10967.0781238764</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0000343200108530477</v>
+        <v>0.0000343548762962215</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00431433767241921</v>
+        <v>0.00431465842523526</v>
       </c>
       <c r="I15" t="n">
-        <v>5925.88590484404</v>
+        <v>5906.117566007</v>
       </c>
       <c r="J15" t="n">
         <v>1000</v>
@@ -982,13 +982,13 @@
         <v>8972.73977642934</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000980385491302219</v>
+        <v>0.0000982091782302409</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00761701534631719</v>
+        <v>0.00764416773516557</v>
       </c>
       <c r="I16" t="n">
-        <v>4849.18960719136</v>
+        <v>4798.44491601081</v>
       </c>
       <c r="J16" t="n">
         <v>1000</v>
@@ -1017,13 +1017,13 @@
         <v>6642.29433679725</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00111524137919043</v>
+        <v>0.00111535057972973</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0243054213972794</v>
+        <v>0.0242942022583521</v>
       </c>
       <c r="I17" t="n">
-        <v>-2071.7933018367</v>
+        <v>-1966.83762194394</v>
       </c>
       <c r="J17" t="n">
         <v>1000</v>
@@ -1052,13 +1052,13 @@
         <v>8363.28367767167</v>
       </c>
       <c r="G18" t="n">
-        <v>0.000357358433194839</v>
+        <v>0.000357637317046423</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0133174701993464</v>
+        <v>0.0133030522984476</v>
       </c>
       <c r="I18" t="n">
-        <v>3007.57979127983</v>
+        <v>3098.86926143932</v>
       </c>
       <c r="J18" t="n">
         <v>1000</v>
@@ -1087,13 +1087,13 @@
         <v>7011.85666483284</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000498918259561767</v>
+        <v>0.000498531039874012</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0158551976615361</v>
+        <v>0.0158658956528862</v>
       </c>
       <c r="I19" t="n">
-        <v>3668.23705211803</v>
+        <v>3730.59330557494</v>
       </c>
       <c r="J19" t="n">
         <v>1000</v>
@@ -1122,13 +1122,13 @@
         <v>-311.893627744737</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0323040058958425</v>
+        <v>0.0340401235620799</v>
       </c>
       <c r="H20" t="n">
-        <v>0.133165204595164</v>
+        <v>0.136455701792049</v>
       </c>
       <c r="I20" t="n">
-        <v>5659.42395481828</v>
+        <v>5671.74571879526</v>
       </c>
       <c r="J20" t="n">
         <v>1000</v>
@@ -1157,13 +1157,13 @@
         <v>10201.3623170357</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0000220798021771321</v>
+        <v>0.0000220758286778471</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00350035100103924</v>
+        <v>0.00350031624878505</v>
       </c>
       <c r="I21" t="n">
-        <v>-1110.60395619706</v>
+        <v>-1853.31135892352</v>
       </c>
       <c r="J21" t="n">
         <v>1000</v>
@@ -1192,13 +1192,13 @@
         <v>10337.5314608963</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0000345066273748728</v>
+        <v>0.000034504478514368</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00431960424717923</v>
+        <v>0.00431956984664171</v>
       </c>
       <c r="I22" t="n">
-        <v>-716.518997323849</v>
+        <v>-1016.93395371286</v>
       </c>
       <c r="J22" t="n">
         <v>1000</v>
@@ -1227,13 +1227,13 @@
         <v>8654.00879149036</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0000985872777896052</v>
+        <v>0.0000985472216988258</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00768163877513591</v>
+        <v>0.00768022841340114</v>
       </c>
       <c r="I23" t="n">
-        <v>-3399.42287972215</v>
+        <v>-3545.68147052504</v>
       </c>
       <c r="J23" t="n">
         <v>1000</v>
@@ -1262,13 +1262,13 @@
         <v>5984.94389661896</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00111471194777673</v>
+        <v>0.00111469686403829</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0242329936897199</v>
+        <v>0.0242335941397127</v>
       </c>
       <c r="I24" t="n">
-        <v>-5724.74860451252</v>
+        <v>-5089.93719689648</v>
       </c>
       <c r="J24" t="n">
         <v>1000</v>
@@ -1297,13 +1297,13 @@
         <v>7725.99514401299</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000360557103639975</v>
+        <v>0.000360581716372196</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0133480962414312</v>
+        <v>0.0133492730468956</v>
       </c>
       <c r="I25" t="n">
-        <v>-3533.238098589</v>
+        <v>-4542.62407350342</v>
       </c>
       <c r="J25" t="n">
         <v>1000</v>
@@ -1332,13 +1332,13 @@
         <v>6608.89314858061</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000499279183675812</v>
+        <v>0.000499332857659875</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0158657040804752</v>
+        <v>0.0158667054091025</v>
       </c>
       <c r="I26" t="n">
-        <v>-5329.9297103264</v>
+        <v>-4678.11138575108</v>
       </c>
       <c r="J26" t="n">
         <v>1000</v>
@@ -1404,10 +1404,10 @@
         <v>8252.12245977249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000354953657072354</v>
+        <v>0.000354956494493566</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0114913980058301</v>
+        <v>0.0114916145174231</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
@@ -1433,10 +1433,10 @@
         <v>-311.893627744737</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0323040058958425</v>
+        <v>0.0340401235620799</v>
       </c>
       <c r="G3" t="n">
-        <v>0.133165204595164</v>
+        <v>0.136455701792049</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1462,10 +1462,10 @@
         <v>8762.16113605591</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000354337667750335</v>
+        <v>0.000354359301181795</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0114861645345081</v>
+        <v>0.0114872701330868</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
@@ -1491,10 +1491,10 @@
         <v>7672.75710017099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000371325988826085</v>
+        <v>0.00036908061721317</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0118303939827653</v>
+        <v>0.0117845885225423</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -1520,10 +1520,10 @@
         <v>8595.43814782061</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000354330147137577</v>
+        <v>0.000354298755930981</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0114769727624113</v>
+        <v>0.011480154573704</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>

--- a/results/consolidated/NF_GARCH_Results_manual.xlsx
+++ b/results/consolidated/NF_GARCH_Results_manual.xlsx
@@ -492,13 +492,13 @@
         <v>9690.38318700543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0000221142231310187</v>
+        <v>0.0000221586308442225</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00350130435394098</v>
+        <v>0.00350657522709918</v>
       </c>
       <c r="I2" t="n">
-        <v>6150.84566075275</v>
+        <v>6091.12355668695</v>
       </c>
       <c r="J2" t="n">
         <v>1000</v>
@@ -527,13 +527,13 @@
         <v>10050.9916224586</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0000342891762629105</v>
+        <v>0.000034380430021123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00430715491474091</v>
+        <v>0.00431437218736813</v>
       </c>
       <c r="I3" t="n">
-        <v>5621.62603480591</v>
+        <v>5568.48559558248</v>
       </c>
       <c r="J3" t="n">
         <v>1000</v>
@@ -562,13 +562,13 @@
         <v>8359.6817151687</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0000982646535001163</v>
+        <v>0.0000985129890248958</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00766466973784182</v>
+        <v>0.00767487245432214</v>
       </c>
       <c r="I4" t="n">
-        <v>4687.23420538713</v>
+        <v>4597.28223830732</v>
       </c>
       <c r="J4" t="n">
         <v>1000</v>
@@ -597,13 +597,13 @@
         <v>5428.81494681033</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00112544275340769</v>
+        <v>0.00112886449992447</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0243310309199076</v>
+        <v>0.0243657221470333</v>
       </c>
       <c r="I5" t="n">
-        <v>2329.32045369707</v>
+        <v>2332.45241615951</v>
       </c>
       <c r="J5" t="n">
         <v>1000</v>
@@ -632,13 +632,13 @@
         <v>6961.90946770692</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000377390286559431</v>
+        <v>0.000380234698186531</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0137695685839832</v>
+        <v>0.0138347283150291</v>
       </c>
       <c r="I6" t="n">
-        <v>3216.14075778238</v>
+        <v>3328.66132101524</v>
       </c>
       <c r="J6" t="n">
         <v>1000</v>
@@ -667,13 +667,13 @@
         <v>5544.76166187601</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000556982610417858</v>
+        <v>0.000564905908803178</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0171338026248393</v>
+        <v>0.0173116921022071</v>
       </c>
       <c r="I7" t="n">
-        <v>3410.28943382607</v>
+        <v>3298.7086956953</v>
       </c>
       <c r="J7" t="n">
         <v>1000</v>
@@ -702,13 +702,13 @@
         <v>10548.1114072935</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000221028496511079</v>
+        <v>0.0000221125950961247</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00350398158196061</v>
+        <v>0.00350258090010257</v>
       </c>
       <c r="I8" t="n">
-        <v>6149.66082564719</v>
+        <v>6126.97657444797</v>
       </c>
       <c r="J8" t="n">
         <v>1000</v>
@@ -737,13 +737,13 @@
         <v>10728.2179537666</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0000343323132413725</v>
+        <v>0.0000343134264060025</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00431244834374611</v>
+        <v>0.00431232536809715</v>
       </c>
       <c r="I9" t="n">
-        <v>5513.45412415785</v>
+        <v>5499.50128709555</v>
       </c>
       <c r="J9" t="n">
         <v>1000</v>
@@ -772,13 +772,13 @@
         <v>8925.63372092964</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000097968589463147</v>
+        <v>0.000097933010840291</v>
       </c>
       <c r="H10" t="n">
-        <v>0.007610469739582</v>
+        <v>0.00761151151521311</v>
       </c>
       <c r="I10" t="n">
-        <v>4678.15826661324</v>
+        <v>4578.68296307645</v>
       </c>
       <c r="J10" t="n">
         <v>1000</v>
@@ -807,13 +807,13 @@
         <v>6314.14340259809</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00111656063919218</v>
+        <v>0.00111465389466928</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0243001199699729</v>
+        <v>0.0242801108181927</v>
       </c>
       <c r="I11" t="n">
-        <v>2332.57302733221</v>
+        <v>2405.97318948381</v>
       </c>
       <c r="J11" t="n">
         <v>1000</v>
@@ -842,13 +842,13 @@
         <v>8098.89143855781</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00035741869281663</v>
+        <v>0.000357254897325573</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0133076321689625</v>
+        <v>0.013288167989599</v>
       </c>
       <c r="I12" t="n">
-        <v>3392.31545946402</v>
+        <v>3574.65152851914</v>
       </c>
       <c r="J12" t="n">
         <v>1000</v>
@@ -877,13 +877,13 @@
         <v>6957.63096377799</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000497409451221445</v>
+        <v>0.000499561834646966</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0158462756380001</v>
+        <v>0.0158725642079564</v>
       </c>
       <c r="I13" t="n">
-        <v>3642.44767713648</v>
+        <v>3534.88880870559</v>
       </c>
       <c r="J13" t="n">
         <v>1000</v>
@@ -912,13 +912,13 @@
         <v>10615.7142367279</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000022072815914142</v>
+        <v>0.0000220734883384139</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00350164442843429</v>
+        <v>0.0034986759293063</v>
       </c>
       <c r="I14" t="n">
-        <v>6197.99496720381</v>
+        <v>6236.36806595074</v>
       </c>
       <c r="J14" t="n">
         <v>1000</v>
@@ -947,13 +947,13 @@
         <v>10967.0781238764</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0000343548762962215</v>
+        <v>0.0000342879023770953</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00431465842523526</v>
+        <v>0.00430993310253984</v>
       </c>
       <c r="I15" t="n">
-        <v>5906.117566007</v>
+        <v>5898.69094610072</v>
       </c>
       <c r="J15" t="n">
         <v>1000</v>
@@ -982,13 +982,13 @@
         <v>8972.73977642934</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000982091782302409</v>
+        <v>0.0000978526990960806</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00764416773516557</v>
+        <v>0.00761288363878511</v>
       </c>
       <c r="I16" t="n">
-        <v>4798.44491601081</v>
+        <v>4844.06105502113</v>
       </c>
       <c r="J16" t="n">
         <v>1000</v>
@@ -1017,13 +1017,13 @@
         <v>6642.29433679725</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00111535057972973</v>
+        <v>0.00111522983045958</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0242942022583521</v>
+        <v>0.0243041801407263</v>
       </c>
       <c r="I17" t="n">
-        <v>-1966.83762194394</v>
+        <v>-2036.78567964723</v>
       </c>
       <c r="J17" t="n">
         <v>1000</v>
@@ -1052,13 +1052,13 @@
         <v>8363.28367767167</v>
       </c>
       <c r="G18" t="n">
-        <v>0.000357637317046423</v>
+        <v>0.000357676173393736</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0133030522984476</v>
+        <v>0.0133166881652794</v>
       </c>
       <c r="I18" t="n">
-        <v>3098.86926143932</v>
+        <v>3041.55719520702</v>
       </c>
       <c r="J18" t="n">
         <v>1000</v>
@@ -1087,13 +1087,13 @@
         <v>7011.85666483284</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000498531039874012</v>
+        <v>0.0004976064836022</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0158658956528862</v>
+        <v>0.0158551210489624</v>
       </c>
       <c r="I19" t="n">
-        <v>3730.59330557494</v>
+        <v>3721.83023101062</v>
       </c>
       <c r="J19" t="n">
         <v>1000</v>
@@ -1122,13 +1122,13 @@
         <v>-311.893627744737</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0340401235620799</v>
+        <v>0.000507650148030649</v>
       </c>
       <c r="H20" t="n">
-        <v>0.136455701792049</v>
+        <v>0.0161296690515369</v>
       </c>
       <c r="I20" t="n">
-        <v>5671.74571879526</v>
+        <v>3535.2605011815</v>
       </c>
       <c r="J20" t="n">
         <v>1000</v>
@@ -1157,13 +1157,13 @@
         <v>10201.3623170357</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0000220758286778471</v>
+        <v>0.0000220780623595792</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00350031624878505</v>
+        <v>0.00350005998084207</v>
       </c>
       <c r="I21" t="n">
-        <v>-1853.31135892352</v>
+        <v>-841.128167265488</v>
       </c>
       <c r="J21" t="n">
         <v>1000</v>
@@ -1192,13 +1192,13 @@
         <v>10337.5314608963</v>
       </c>
       <c r="G22" t="n">
-        <v>0.000034504478514368</v>
+        <v>0.00003450217978867</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00431956984664171</v>
+        <v>0.00431935149035112</v>
       </c>
       <c r="I22" t="n">
-        <v>-1016.93395371286</v>
+        <v>-740.941689798181</v>
       </c>
       <c r="J22" t="n">
         <v>1000</v>
@@ -1227,13 +1227,13 @@
         <v>8654.00879149036</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0000985472216988258</v>
+        <v>0.0000985879822252114</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00768022841340114</v>
+        <v>0.00768180191168424</v>
       </c>
       <c r="I23" t="n">
-        <v>-3545.68147052504</v>
+        <v>-2675.00782728108</v>
       </c>
       <c r="J23" t="n">
         <v>1000</v>
@@ -1262,13 +1262,13 @@
         <v>5984.94389661896</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00111469686403829</v>
+        <v>0.001114776146248</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0242335941397127</v>
+        <v>0.0242357836266807</v>
       </c>
       <c r="I24" t="n">
-        <v>-5089.93719689648</v>
+        <v>-5945.51191729431</v>
       </c>
       <c r="J24" t="n">
         <v>1000</v>
@@ -1297,13 +1297,13 @@
         <v>7725.99514401299</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000360581716372196</v>
+        <v>0.000360516319778998</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0133492730468956</v>
+        <v>0.0133480200879298</v>
       </c>
       <c r="I25" t="n">
-        <v>-4542.62407350342</v>
+        <v>-4160.60447744878</v>
       </c>
       <c r="J25" t="n">
         <v>1000</v>
@@ -1332,13 +1332,13 @@
         <v>6608.89314858061</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000499332857659875</v>
+        <v>0.000499331428163572</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0158667054091025</v>
+        <v>0.0158667967078021</v>
       </c>
       <c r="I26" t="n">
-        <v>-4678.11138575108</v>
+        <v>-4888.94348585455</v>
       </c>
       <c r="J26" t="n">
         <v>1000</v>
@@ -1404,10 +1404,10 @@
         <v>8252.12245977249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000354956494493566</v>
+        <v>0.000354965353094005</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0114916145174231</v>
+        <v>0.0114919689675483</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
@@ -1433,10 +1433,10 @@
         <v>-311.893627744737</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0340401235620799</v>
+        <v>0.000507650148030649</v>
       </c>
       <c r="G3" t="n">
-        <v>0.136455701792049</v>
+        <v>0.0161296690515369</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1462,10 +1462,10 @@
         <v>8762.16113605591</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000354359301181795</v>
+        <v>0.000354121096211184</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0114872701330868</v>
+        <v>0.0114829136709332</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
@@ -1491,10 +1491,10 @@
         <v>7672.75710017099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00036908061721317</v>
+        <v>0.00037150952613407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0117845885225423</v>
+        <v>0.0118346604055098</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -1520,10 +1520,10 @@
         <v>8595.43814782061</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000354298755930981</v>
+        <v>0.00035430494316404</v>
       </c>
       <c r="G6" t="n">
-        <v>0.011480154573704</v>
+        <v>0.0114778767998602</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>

--- a/results/consolidated/NF_GARCH_Results_manual.xlsx
+++ b/results/consolidated/NF_GARCH_Results_manual.xlsx
@@ -75,10 +75,10 @@
     <t xml:space="preserve">AMZN</t>
   </si>
   <si>
-    <t xml:space="preserve">sstd</t>
-  </si>
-  <si>
     <t xml:space="preserve">gjrGARCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">std</t>
   </si>
   <si>
     <t xml:space="preserve">eGARCH</t>
@@ -684,31 +684,31 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>-21086.222814587</v>
+        <v>-21219.4284734558</v>
       </c>
       <c r="E8" t="n">
-        <v>-21056.3022047935</v>
+        <v>-21183.5237417036</v>
       </c>
       <c r="F8" t="n">
-        <v>10548.1114072935</v>
+        <v>10615.7142367279</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000221125950961247</v>
+        <v>0.0000220899886058771</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00350258090010257</v>
+        <v>0.00350315431501287</v>
       </c>
       <c r="I8" t="n">
-        <v>6126.97657444797</v>
+        <v>6223.74448177264</v>
       </c>
       <c r="J8" t="n">
         <v>1000</v>
@@ -719,31 +719,31 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-21446.4359075332</v>
+        <v>-21922.1562477529</v>
       </c>
       <c r="E9" t="n">
-        <v>-21416.5152977397</v>
+        <v>-21886.2515160007</v>
       </c>
       <c r="F9" t="n">
-        <v>10728.2179537666</v>
+        <v>10967.0781238764</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0000343134264060025</v>
+        <v>0.0000342964198041262</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00431232536809715</v>
+        <v>0.00431375960712445</v>
       </c>
       <c r="I9" t="n">
-        <v>5499.50128709555</v>
+        <v>5902.8244011558</v>
       </c>
       <c r="J9" t="n">
         <v>1000</v>
@@ -754,31 +754,31 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-17841.2674418593</v>
+        <v>-17933.4795528587</v>
       </c>
       <c r="E10" t="n">
-        <v>-17811.3468320658</v>
+        <v>-17897.5748211065</v>
       </c>
       <c r="F10" t="n">
-        <v>8925.63372092964</v>
+        <v>8972.73977642934</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000097933010840291</v>
+        <v>0.000098089951593645</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00761151151521311</v>
+        <v>0.00761853085890284</v>
       </c>
       <c r="I10" t="n">
-        <v>4578.68296307645</v>
+        <v>4861.56207368077</v>
       </c>
       <c r="J10" t="n">
         <v>1000</v>
@@ -789,31 +789,31 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-12618.2868051962</v>
+        <v>-13272.5886735945</v>
       </c>
       <c r="E11" t="n">
-        <v>-12588.3661954027</v>
+        <v>-13236.6839418423</v>
       </c>
       <c r="F11" t="n">
-        <v>6314.14340259809</v>
+        <v>6642.29433679725</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00111465389466928</v>
+        <v>0.00111534537444763</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0242801108181927</v>
+        <v>0.0243047025513129</v>
       </c>
       <c r="I11" t="n">
-        <v>2405.97318948381</v>
+        <v>-2067.25897115705</v>
       </c>
       <c r="J11" t="n">
         <v>1000</v>
@@ -824,31 +824,31 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-16187.7828771156</v>
+        <v>-16714.5673553433</v>
       </c>
       <c r="E12" t="n">
-        <v>-16157.8622673221</v>
+        <v>-16678.6626235911</v>
       </c>
       <c r="F12" t="n">
-        <v>8098.89143855781</v>
+        <v>8363.28367767167</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000357254897325573</v>
+        <v>0.000357402335537457</v>
       </c>
       <c r="H12" t="n">
-        <v>0.013288167989599</v>
+        <v>0.0133117347345129</v>
       </c>
       <c r="I12" t="n">
-        <v>3574.65152851914</v>
+        <v>3037.58715489622</v>
       </c>
       <c r="J12" t="n">
         <v>1000</v>
@@ -859,31 +859,31 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-13905.261927556</v>
+        <v>-14011.7133296657</v>
       </c>
       <c r="E13" t="n">
-        <v>-13875.3413177625</v>
+        <v>-13975.8085979135</v>
       </c>
       <c r="F13" t="n">
-        <v>6957.63096377799</v>
+        <v>7011.85666483284</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000499561834646966</v>
+        <v>0.000498049718244985</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0158725642079564</v>
+        <v>0.0158566907824145</v>
       </c>
       <c r="I13" t="n">
-        <v>3534.88880870559</v>
+        <v>3728.01895383072</v>
       </c>
       <c r="J13" t="n">
         <v>1000</v>
@@ -894,31 +894,31 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>-21219.4284734558</v>
+        <v>635.787255489474</v>
       </c>
       <c r="E14" t="n">
-        <v>-21183.5237417036</v>
+        <v>671.691987241692</v>
       </c>
       <c r="F14" t="n">
-        <v>10615.7142367279</v>
+        <v>-311.893627744737</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0000220734883384139</v>
+        <v>0.000505830603863818</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0034986759293063</v>
+        <v>0.0160926632878579</v>
       </c>
       <c r="I14" t="n">
-        <v>6236.36806595074</v>
+        <v>3529.32316862138</v>
       </c>
       <c r="J14" t="n">
         <v>1000</v>
@@ -929,31 +929,31 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>-21922.1562477529</v>
+        <v>-20390.7246340714</v>
       </c>
       <c r="E15" t="n">
-        <v>-21886.2515160007</v>
+        <v>-20354.8199023192</v>
       </c>
       <c r="F15" t="n">
-        <v>10967.0781238764</v>
+        <v>10201.3623170357</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0000342879023770953</v>
+        <v>0.0000220806815155538</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00430993310253984</v>
+        <v>0.00350059548461617</v>
       </c>
       <c r="I15" t="n">
-        <v>5898.69094610072</v>
+        <v>-1211.44723357436</v>
       </c>
       <c r="J15" t="n">
         <v>1000</v>
@@ -964,31 +964,31 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>-17933.4795528587</v>
+        <v>-20663.0629217926</v>
       </c>
       <c r="E16" t="n">
-        <v>-17897.5748211065</v>
+        <v>-20627.1581900404</v>
       </c>
       <c r="F16" t="n">
-        <v>8972.73977642934</v>
+        <v>10337.5314608963</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000978526990960806</v>
+        <v>0.0000345046057821764</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00761288363878511</v>
+        <v>0.00431957891814382</v>
       </c>
       <c r="I16" t="n">
-        <v>4844.06105502113</v>
+        <v>-803.811410289445</v>
       </c>
       <c r="J16" t="n">
         <v>1000</v>
@@ -999,31 +999,31 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>-13272.5886735945</v>
+        <v>-17296.0175829807</v>
       </c>
       <c r="E17" t="n">
-        <v>-13236.6839418423</v>
+        <v>-17260.1128512285</v>
       </c>
       <c r="F17" t="n">
-        <v>6642.29433679725</v>
+        <v>8654.00879149036</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00111522983045958</v>
+        <v>0.0000985764594588027</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0243041801407263</v>
+        <v>0.00768124969168561</v>
       </c>
       <c r="I17" t="n">
-        <v>-2036.78567964723</v>
+        <v>-2819.25534825357</v>
       </c>
       <c r="J17" t="n">
         <v>1000</v>
@@ -1034,31 +1034,31 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>-16714.5673553433</v>
+        <v>-11957.8877932379</v>
       </c>
       <c r="E18" t="n">
-        <v>-16678.6626235911</v>
+        <v>-11921.9830614857</v>
       </c>
       <c r="F18" t="n">
-        <v>8363.28367767167</v>
+        <v>5984.94389661896</v>
       </c>
       <c r="G18" t="n">
-        <v>0.000357676173393736</v>
+        <v>0.00111480004288859</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0133166881652794</v>
+        <v>0.0242348350428466</v>
       </c>
       <c r="I18" t="n">
-        <v>3041.55719520702</v>
+        <v>-6011.46874657578</v>
       </c>
       <c r="J18" t="n">
         <v>1000</v>
@@ -1069,31 +1069,31 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>-14011.7133296657</v>
+        <v>-15439.990288026</v>
       </c>
       <c r="E19" t="n">
-        <v>-13975.8085979135</v>
+        <v>-15404.0855562738</v>
       </c>
       <c r="F19" t="n">
-        <v>7011.85666483284</v>
+        <v>7725.99514401299</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004976064836022</v>
+        <v>0.000360533639688918</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0158551210489624</v>
+        <v>0.0133476875206534</v>
       </c>
       <c r="I19" t="n">
-        <v>3721.83023101062</v>
+        <v>-3639.58444911581</v>
       </c>
       <c r="J19" t="n">
         <v>1000</v>
@@ -1104,246 +1104,36 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>635.787255489474</v>
+        <v>-13205.7862971612</v>
       </c>
       <c r="E20" t="n">
-        <v>671.691987241692</v>
+        <v>-13169.881565409</v>
       </c>
       <c r="F20" t="n">
-        <v>-311.893627744737</v>
+        <v>6608.89314858061</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000507650148030649</v>
+        <v>0.000499299334420236</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0161296690515369</v>
+        <v>0.0158651585390775</v>
       </c>
       <c r="I20" t="n">
-        <v>3535.2605011815</v>
+        <v>-5132.65281526239</v>
       </c>
       <c r="J20" t="n">
         <v>1000</v>
       </c>
       <c r="K20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-20390.7246340714</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-20354.8199023192</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10201.3623170357</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0000220780623595792</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.00350005998084207</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-841.128167265488</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-20663.0629217926</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-20627.1581900404</v>
-      </c>
-      <c r="F22" t="n">
-        <v>10337.5314608963</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.00003450217978867</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00431935149035112</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-740.941689798181</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-17296.0175829807</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-17260.1128512285</v>
-      </c>
-      <c r="F23" t="n">
-        <v>8654.00879149036</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.0000985879822252114</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00768180191168424</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-2675.00782728108</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-11957.8877932379</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-11921.9830614857</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5984.94389661896</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.001114776146248</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.0242357836266807</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-5945.51191729431</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-15439.990288026</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-15404.0855562738</v>
-      </c>
-      <c r="F25" t="n">
-        <v>7725.99514401299</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.000360516319778998</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.0133480200879298</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-4160.60447744878</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-13205.7862971612</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-13169.881565409</v>
-      </c>
-      <c r="F26" t="n">
-        <v>6608.89314858061</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.000499331428163572</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.0158667967078021</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-4888.94348585455</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K26" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1392,7 +1182,7 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>-16492.244919545</v>
@@ -1404,10 +1194,10 @@
         <v>8252.12245977249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000354965353094005</v>
+        <v>0.000354965793959046</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0114919689675483</v>
+        <v>0.0114915175328372</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
@@ -1421,7 +1211,7 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>635.787255489474</v>
@@ -1433,10 +1223,10 @@
         <v>-311.893627744737</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000507650148030649</v>
+        <v>0.000505830603863818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0161296690515369</v>
+        <v>0.0160926632878579</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1447,10 +1237,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>-17512.3222721118</v>
@@ -1462,10 +1252,10 @@
         <v>8762.16113605591</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000354121096211184</v>
+        <v>0.000354212298038954</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0114829136709332</v>
+        <v>0.0114847621415467</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
@@ -1500,35 +1290,6 @@
         <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-17180.8762956412</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-17150.9556858477</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8595.43814782061</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.00035430494316404</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.0114778767998602</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
         <v>31</v>
       </c>
     </row>

--- a/results/consolidated/NF_GARCH_Results_manual.xlsx
+++ b/results/consolidated/NF_GARCH_Results_manual.xlsx
@@ -492,16 +492,16 @@
         <v>9690.38318700543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0000221586308442225</v>
+        <v>0.0000221502614205928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00350657522709918</v>
+        <v>0.00350098170754738</v>
       </c>
       <c r="I2" t="n">
-        <v>6091.12355668695</v>
+        <v>5964.7368220389</v>
       </c>
       <c r="J2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K2" t="s">
         <v>14</v>
@@ -527,16 +527,16 @@
         <v>10050.9916224586</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000034380430021123</v>
+        <v>0.0000345178681459439</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00431437218736813</v>
+        <v>0.00432795002506048</v>
       </c>
       <c r="I3" t="n">
-        <v>5568.48559558248</v>
+        <v>5347.30986735</v>
       </c>
       <c r="J3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K3" t="s">
         <v>14</v>
@@ -562,16 +562,16 @@
         <v>8359.6817151687</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0000985129890248958</v>
+        <v>0.0000993909985205136</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00767487245432214</v>
+        <v>0.00771464216274853</v>
       </c>
       <c r="I4" t="n">
-        <v>4597.28223830732</v>
+        <v>4479.01481686913</v>
       </c>
       <c r="J4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K4" t="s">
         <v>14</v>
@@ -597,16 +597,16 @@
         <v>5428.81494681033</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00112886449992447</v>
+        <v>0.00113136808173854</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0243657221470333</v>
+        <v>0.0244007186754356</v>
       </c>
       <c r="I5" t="n">
-        <v>2332.45241615951</v>
+        <v>2207.29395744856</v>
       </c>
       <c r="J5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K5" t="s">
         <v>14</v>
@@ -632,16 +632,16 @@
         <v>6961.90946770692</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000380234698186531</v>
+        <v>0.000379916596518305</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0138347283150291</v>
+        <v>0.0138335473655937</v>
       </c>
       <c r="I6" t="n">
-        <v>3328.66132101524</v>
+        <v>3198.3897728614</v>
       </c>
       <c r="J6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K6" t="s">
         <v>14</v>
@@ -667,16 +667,16 @@
         <v>5544.76166187601</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000564905908803178</v>
+        <v>0.000567348149496385</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0173116921022071</v>
+        <v>0.0173647390090551</v>
       </c>
       <c r="I7" t="n">
-        <v>3298.7086956953</v>
+        <v>3153.80400473469</v>
       </c>
       <c r="J7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K7" t="s">
         <v>14</v>
@@ -702,16 +702,16 @@
         <v>10615.7142367279</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000220899886058771</v>
+        <v>0.0000223615885486666</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00350315431501287</v>
+        <v>0.00353185265624556</v>
       </c>
       <c r="I8" t="n">
-        <v>6223.74448177264</v>
+        <v>6134.05590876226</v>
       </c>
       <c r="J8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K8" t="s">
         <v>14</v>
@@ -737,16 +737,16 @@
         <v>10967.0781238764</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0000342964198041262</v>
+        <v>0.0000344300611238395</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00431375960712445</v>
+        <v>0.0043345000740643</v>
       </c>
       <c r="I9" t="n">
-        <v>5902.8244011558</v>
+        <v>5835.55752941045</v>
       </c>
       <c r="J9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K9" t="s">
         <v>14</v>
@@ -772,16 +772,16 @@
         <v>8972.73977642934</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000098089951593645</v>
+        <v>0.000097968623664851</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00761853085890284</v>
+        <v>0.00762478844455467</v>
       </c>
       <c r="I10" t="n">
-        <v>4861.56207368077</v>
+        <v>4771.47952131575</v>
       </c>
       <c r="J10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K10" t="s">
         <v>14</v>
@@ -807,16 +807,16 @@
         <v>6642.29433679725</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00111534537444763</v>
+        <v>0.00111568314532112</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0243047025513129</v>
+        <v>0.0243210237958923</v>
       </c>
       <c r="I11" t="n">
-        <v>-2067.25897115705</v>
+        <v>-695.0019926656</v>
       </c>
       <c r="J11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K11" t="s">
         <v>14</v>
@@ -842,16 +842,16 @@
         <v>8363.28367767167</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000357402335537457</v>
+        <v>0.000356706471914379</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0133117347345129</v>
+        <v>0.0132974872468535</v>
       </c>
       <c r="I12" t="n">
-        <v>3037.58715489622</v>
+        <v>3197.58996884358</v>
       </c>
       <c r="J12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K12" t="s">
         <v>14</v>
@@ -877,16 +877,16 @@
         <v>7011.85666483284</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000498049718244985</v>
+        <v>0.000502462606266766</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0158566907824145</v>
+        <v>0.0159696312552844</v>
       </c>
       <c r="I13" t="n">
-        <v>3728.01895383072</v>
+        <v>3639.22496904861</v>
       </c>
       <c r="J13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K13" t="s">
         <v>14</v>
@@ -912,16 +912,16 @@
         <v>-311.893627744737</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000505830603863818</v>
+        <v>0.000553297503494059</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0160926632878579</v>
+        <v>0.0172362186738709</v>
       </c>
       <c r="I14" t="n">
-        <v>3529.32316862138</v>
+        <v>3496.4065642525</v>
       </c>
       <c r="J14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K14" t="s">
         <v>14</v>
@@ -947,16 +947,16 @@
         <v>10201.3623170357</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0000220806815155538</v>
+        <v>0.0000220786970132616</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00350059548461617</v>
+        <v>0.0035002379434319</v>
       </c>
       <c r="I15" t="n">
-        <v>-1211.44723357436</v>
+        <v>2253.61726177711</v>
       </c>
       <c r="J15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K15" t="s">
         <v>14</v>
@@ -982,16 +982,16 @@
         <v>10337.5314608963</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000345046057821764</v>
+        <v>0.0000345013235870406</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00431957891814382</v>
+        <v>0.00431928121262559</v>
       </c>
       <c r="I16" t="n">
-        <v>-803.811410289445</v>
+        <v>2341.25927651771</v>
       </c>
       <c r="J16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K16" t="s">
         <v>14</v>
@@ -1017,16 +1017,16 @@
         <v>8654.00879149036</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0000985764594588027</v>
+        <v>0.0000985475241770422</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00768124969168561</v>
+        <v>0.00768033438730387</v>
       </c>
       <c r="I17" t="n">
-        <v>-2819.25534825357</v>
+        <v>621.379306545768</v>
       </c>
       <c r="J17" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K17" t="s">
         <v>14</v>
@@ -1052,16 +1052,16 @@
         <v>5984.94389661896</v>
       </c>
       <c r="G18" t="n">
-        <v>0.00111480004288859</v>
+        <v>0.0011147216977999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0242348350428466</v>
+        <v>0.0242338278694657</v>
       </c>
       <c r="I18" t="n">
-        <v>-6011.46874657578</v>
+        <v>-2224.45731256715</v>
       </c>
       <c r="J18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K18" t="s">
         <v>14</v>
@@ -1087,16 +1087,16 @@
         <v>7725.99514401299</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000360533639688918</v>
+        <v>0.000360542263970232</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0133476875206534</v>
+        <v>0.0133511357442286</v>
       </c>
       <c r="I19" t="n">
-        <v>-3639.58444911581</v>
+        <v>-502.603671654493</v>
       </c>
       <c r="J19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K19" t="s">
         <v>14</v>
@@ -1122,16 +1122,16 @@
         <v>6608.89314858061</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000499299334420236</v>
+        <v>0.000499492774893839</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0158651585390775</v>
+        <v>0.0158690506333466</v>
       </c>
       <c r="I20" t="n">
-        <v>-5132.65281526239</v>
+        <v>-1206.52535084575</v>
       </c>
       <c r="J20" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K20" t="s">
         <v>14</v>
@@ -1194,10 +1194,10 @@
         <v>8252.12245977249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000354965793959046</v>
+        <v>0.000354980713573553</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0114915175328372</v>
+        <v>0.0114923112984004</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
@@ -1223,10 +1223,10 @@
         <v>-311.893627744737</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000505830603863818</v>
+        <v>0.000553297503494059</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0160926632878579</v>
+        <v>0.0172362186738709</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1252,10 +1252,10 @@
         <v>8762.16113605591</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000354212298038954</v>
+        <v>0.000354935416139936</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0114847621415467</v>
+        <v>0.0115132139121491</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
@@ -1281,10 +1281,10 @@
         <v>7672.75710017099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00037150952613407</v>
+        <v>0.000372448659306713</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0118346604055098</v>
+        <v>0.0118570964909068</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
